--- a/output/04_SOURCE_REGISTER_v1.0.xlsx
+++ b/output/04_SOURCE_REGISTER_v1.0.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy_Map" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$T$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$T$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -87,6 +87,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
@@ -98,11 +103,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T65"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M3" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>Planned: Ch 2</t>
+          <t>Ch 2.3</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
@@ -1533,7 +1533,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr"/>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>The second client extraction states 51% affordable or at a stretch and 49% unaffordable, which does not follow from its own figures (22% + 27% = 49%). The register keeps 51% not affordable; check against the report.</t>
+        </is>
+      </c>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="inlineStr"/>
     </row>
@@ -1575,7 +1579,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -1596,7 +1600,7 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
@@ -1661,7 +1665,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -1682,7 +1686,7 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -1697,7 +1701,7 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>Planned: Ch 2</t>
+          <t>Ch 2.3</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -1707,7 +1711,7 @@
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>DEFINITION TO VERIFY: the global split (22% + 27% = 49%) is incremental; it must be checked whether 46% for Sub-Saharan Africa is incremental or cumulative (16% included).</t>
+          <t>DEFINITION TO VERIFY: the global split (22% + 27% = 49%) is incremental. The second client extraction reads 46% as additional to 16% (62% in total); to check in the report. Not to be confused with the 62% average collection rate (E1-14).</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr"/>
@@ -1749,7 +1753,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -1770,7 +1774,7 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
@@ -1835,7 +1839,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -1856,7 +1860,7 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
@@ -1871,7 +1875,7 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>Planned: Ch 5 (cost to serve)</t>
+          <t>Ch 5.6</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -1921,7 +1925,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1942,7 +1946,7 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
@@ -1990,7 +1994,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>2021-2023 (book says 2023: period to verify)</t>
+          <t>2021-2023 (reported as stable at about 62% over the period)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -2005,7 +2009,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -2026,7 +2030,7 @@
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
@@ -2041,7 +2045,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>Ch 1.6, 7.4, 15 (as 'about 62% in 2023', secondary caveat)</t>
+          <t>Ch 1.6, 7.4, 15, 16 (as about 62% from 2021 to 2023, reported)</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -2051,7 +2055,7 @@
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>A collection rate, not the PAYGo PERFORM 2026 Repayment Rate. Definition (numerator, denominator, deposits, weighting) to verify before any comparison with the model's operational collection rate.</t>
+          <t>Both client extractions give the average as about 62% across 2021 to 2023; earlier search snippets gave 62% in 2023, in line with 2021. The book says the rate stayed at about 62% over 2021 to 2023, which fits both readings. Reported definition: payments received over payments expected in the period. A collection rate, not the PAYGo PERFORM 2026 Repayment Rate. Definition (numerator, denominator, deposits, weighting) to verify before any comparison with the model's operational collection rate.</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
@@ -2103,7 +2107,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -2124,7 +2128,7 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>Planned: Ch 7.4</t>
+          <t>Ch 1.6, 7.4</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -2189,7 +2193,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -2210,7 +2214,7 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
@@ -2225,7 +2229,7 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>Ch 1.6, 7.4, 15 currently say 'about half of PAYGo customers had been written off or were more than 30 days late'</t>
+          <t>Ch 1.6, 15 (as half of companies, reported)</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2235,7 +2239,7 @@
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>CONFLICTS WITH THE BOOK'S WORDING: the client extraction concerns half of companies within a ratio band, not half of customers. Book wording to be withdrawn. RAR30 and write-off ratio are 2021 PERFORM portfolio quality metrics (E2a-03, E2a-04).</t>
+          <t>Both client extractions concern half of companies within a ratio band, not half of customers; the earlier book wording about customers has been withdrawn. RAR30 and write-off ratio are 2021 PERFORM portfolio quality metrics (E2a-03, E2a-04).</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr"/>
@@ -2279,7 +2283,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -2300,7 +2304,7 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
@@ -2367,7 +2371,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -2388,7 +2392,7 @@
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
@@ -2453,7 +2457,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -2474,7 +2478,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
@@ -2489,7 +2493,7 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>Planned: Ch 10, 11, 12</t>
+          <t>Ch 11.3</t>
         </is>
       </c>
       <c r="Q20" s="7" t="inlineStr">
@@ -2539,7 +2543,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -2560,7 +2564,7 @@
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
@@ -2625,7 +2629,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -2646,7 +2650,7 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
@@ -2711,7 +2715,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -2732,7 +2736,7 @@
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
@@ -2797,7 +2801,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -2818,7 +2822,7 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
@@ -2833,7 +2837,7 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>Planned: Ch 13</t>
+          <t>Ch 13.1</t>
         </is>
       </c>
       <c r="Q24" s="7" t="inlineStr">
@@ -2853,7 +2857,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Financing need to serve, by 2030, the 398 million people for whom off-grid solar is the least-cost option (about 41% of households to be electrified)</t>
+          <t>Financing need to serve, by 2030, the 398 million people for whom off-grid solar is the least-cost option (about 41% of the about 969 million people to be electrified)</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -2883,7 +2887,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -2904,7 +2908,7 @@
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
@@ -2919,7 +2923,7 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>Planned: Ch 1, 13</t>
+          <t>Ch 13.7</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -2929,7 +2933,7 @@
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>About half public, half private; public funding from about USD 1bn in 2025 to about USD 2.1bn a year in 2028-2030; governments about 30-40% of total cost (client extraction).</t>
+          <t>About half public, half private; public funding from about USD 1bn in 2025 to about USD 2.1bn a year in 2028-2030; governments about 30-40% of total cost (client extraction). The register previously read 41% of households; the second extraction gives 41% of people.</t>
         </is>
       </c>
       <c r="S25" s="7" t="inlineStr"/>
@@ -2948,7 +2952,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>216 million (about 55%), about USD 9bn</t>
+          <t>216 million (about 54%), about USD 9bn</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -2973,7 +2977,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>2024 (month to verify)</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -2994,7 +2998,7 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>Client extraction from the report, 3 Oct 2026; primary PDF not held</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
@@ -3022,425 +3026,421 @@
       <c r="T26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>E2-01</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>The PAYGo PERFORM KPIs are five: RR Paid vs Plan (PvP); RR Paid vs Financed (PvFin); RR PvP @90 Days; RR PvP @2x; Ownership Rate @2x</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>5 KPIs</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>GOGLA (PAYGo PERFORM initiative)</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>Summary Guide: KPI Definitions, Formulas &amp; Key Calculation Rules</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>Industry standard, read in the project file</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>E1-26</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Share of PAYGo customers facing payment difficulties</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>about 1 in 4 (fewer than 1 in 5 about four years earlier)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>share of customers</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Off-Grid Solar Market Trends Report 2024</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>ESMAP / World Bank, with GOGLA and Dalberg (as reported)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>MTR 2024 (primary PDF not held by the project)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.esmap.org/sites/default/files/esmap-files/2024-Off-Grid-Solar-Market-Trends-Report.pdf (not opened from this environment)</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>Ch 7 (to be restructured), Annex A</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t>Planned PERFORM 2026 block (change M3)</t>
-        </is>
-      </c>
-      <c r="R27" s="8" t="inlineStr"/>
-      <c r="S27" s="8" t="inlineStr"/>
-      <c r="T27" s="8" t="inlineStr"/>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>Ch 7.4</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>Second client extraction, 4 Oct 2026. Definition of payment difficulty to verify.</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>E2-02</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Collection Rate and other substitute metrics must not be used in place of the Repayment Rate calculation; the only accepted alternative basis is cumulative arrears</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>GOGLA (PAYGo PERFORM initiative)</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>Repayment Rate: Core Calculation Rules, rule 3A and 3B</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>Industry standard, read in the project file</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>E1-27</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Affordability method assumptions for a Tier 1 PAYGo product: 20% deposit, 2 year repayment, 40% annual interest</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>20% / 2 years / 40%</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Off-Grid Solar Market Trends Report 2024</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>ESMAP / World Bank, with GOGLA and Dalberg (as reported)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>MTR 2024 (primary PDF not held by the project)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>https://www.esmap.org/sites/default/files/esmap-files/2024-Off-Grid-Solar-Market-Trends-Report.pdf (not opened from this environment)</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="inlineStr">
-        <is>
-          <t>Ch 7</t>
-        </is>
-      </c>
-      <c r="Q28" s="8" t="inlineStr">
-        <is>
-          <t>KPIs labels (change M3)</t>
-        </is>
-      </c>
-      <c r="R28" s="8" t="inlineStr"/>
-      <c r="S28" s="8" t="inlineStr"/>
-      <c r="T28" s="8" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>Ch 2.3</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>Assumptions of the report's method, not market evidence. Reported cash prices of USD 71.61 (urban) and USD 198.75 (rural), 2017 PPP dollars, and USD 465 for Tier 2, to verify.</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>E2-03</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Repayment Rate rules: excludes deposits and prepayments; includes arrears payments and write-offs; cumulative since contract start after any free-use period; instalments normalised to daily equivalents; payments recognised pro rata when applied to due instalments</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>rules</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>GOGLA (PAYGo PERFORM initiative)</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>9-10</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>Repayment Rate: Definition, Formula; Core Calculation Rules</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t>Industry standard, read in the project file</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>E1-28</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Composition of the about USD 21.3bn universal access need: debt, equity, grants, affordability gap (the gap associated with about 240 million people)</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>6.4 / 4.3 / 1.5 / 9.2</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>USD bn</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2025-2030</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Off-Grid Solar Market Trends Report 2024</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>ESMAP / World Bank, with GOGLA and Dalberg (as reported)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>MTR 2024 (primary PDF not held by the project)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.esmap.org/sites/default/files/esmap-files/2024-Off-Grid-Solar-Market-Trends-Report.pdf (not opened from this environment)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="inlineStr">
-        <is>
-          <t>Ch 6, 7</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t>Planned PERFORM 2026 block (change M3)</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr"/>
-      <c r="S29" s="8" t="inlineStr"/>
-      <c r="T29" s="8" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>Ch 13.7</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>Internal check: the components add to USD 21.4bn against a stated USD 21.3bn (rounding to verify); 240 of 398 million is about 60%, stated as about 59%.</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr"/>
+      <c r="T29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>E2-04</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Ownership Rate @2x: proportion of contracts fully paid as of twice the contract term, among contracts that have reached at least 2x</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>GOGLA (PAYGo PERFORM initiative)</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>8; 16-18</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>Ownership Rate</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>Industry standard, read in the project file</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>E1-29</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Local currency debt financing as a share of off-grid solar investment, 2017-2023 average</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>about 20%</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>% of investment</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>2017-2023</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Off-Grid Solar Market Trends Report 2024</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>ESMAP / World Bank, with GOGLA and Dalberg (as reported)</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>MTR 2024 (primary PDF not held by the project)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>https://www.esmap.org/sites/default/files/esmap-files/2024-Off-Grid-Solar-Market-Trends-Report.pdf (not opened from this environment)</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="P30" s="8" t="inlineStr">
-        <is>
-          <t>Ch 7, 13</t>
-        </is>
-      </c>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>Vintage_Dashboard, RBF_Engine (ownership-linked RBF)</t>
-        </is>
-      </c>
-      <c r="R30" s="8" t="inlineStr"/>
-      <c r="S30" s="8" t="inlineStr"/>
-      <c r="T30" s="8" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>Ch 11.3</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr"/>
+      <c r="T30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>E2-05</t>
+          <t>E1-30</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>At a Glance companion: core RR calculation rules (1) exclude deposits (2) exclude prepayments (3) include arrears payments (4) include write-offs (5) cumulative since contract start</t>
+          <t>World Bank lending to governments for off-grid solar, FY2024</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>rules</t>
+          <t>about 660 or 626</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>USD m</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM KPIs, At a Glance</t>
+          <t>Off-Grid Solar Market Trends Report 2024</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>GOGLA (PAYGo PERFORM initiative)</t>
+          <t>ESMAP / World Bank, with GOGLA and Dalberg (as reported)</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>October 2024 (as reported in the client extractions; to verify)</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>70d4c519-PAYGo-PERFORM-KPIs_At-A-Glance_2026.pdf (12 pages)</t>
+          <t>MTR 2024 (primary PDF not held by the project)</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>PAGE TO VERIFY</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr"/>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
+          <t>https://www.esmap.org/sites/default/files/esmap-files/2024-Off-Grid-Solar-Market-Trends-Report.pdf (not opened from this environment)</t>
         </is>
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>Industry standard, read in the project file</t>
+          <t>Client extractions from the report, 3 Oct 2026 and 4 Oct 2026 (the second gives chapter page ranges only, not pages per figure); primary PDF not held</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONFLICTING SOURCES</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>Ch 7</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Q31" s="8" t="inlineStr">
@@ -3463,24 +3463,28 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr"/>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>The second client extraction reports both figures in different sections of the report. Not used until checked in the document.</t>
+        </is>
+      </c>
       <c r="S31" s="8" t="inlineStr"/>
       <c r="T31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>E2-06</t>
+          <t>E2-01</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM framework attributed to CGAP, GOGLA and Lighting Global with collection rate and receivables at risk as framework KPIs</t>
+          <t>The PAYGo PERFORM KPIs are five: RR Paid vs Plan (PvP); RR Paid vs Financed (PvFin); RR PvP @90 Days; RR PvP @2x; Ownership Rate @2x</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>framework</t>
+          <t>5 KPIs</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -3490,43 +3494,47 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>CGAP, GOGLA, IFC Lighting Global</t>
+          <t>GOGLA (PAYGo PERFORM initiative)</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>July 2021</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Front matter</t>
-        </is>
-      </c>
-      <c r="K32" s="9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>Summary Guide: KPI Definitions, Formulas &amp; Key Calculation Rules</t>
+        </is>
+      </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+          <t>Project file (uploaded 3 Oct 2026)</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>Industry standard (superseded), read in the project file</t>
+          <t>Industry standard, read in the project file</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
@@ -3536,45 +3544,37 @@
       </c>
       <c r="O32" s="9" t="inlineStr">
         <is>
-          <t>VERIFIED (HISTORICAL)</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P32" s="9" t="inlineStr">
         <is>
-          <t>Ch 7.1</t>
+          <t>Ch 7 (to be restructured), Annex A</t>
         </is>
       </c>
       <c r="Q32" s="9" t="inlineStr">
         <is>
-          <t>Previous register entry (SR21) replaced by E2-01 to E2-05 and E2a</t>
-        </is>
-      </c>
-      <c r="R32" s="9" t="inlineStr">
-        <is>
-          <t>The 2021 framing is historical; the current standard is E2 (June 2026).</t>
-        </is>
-      </c>
+          <t>Planned PERFORM 2026 block (change M3)</t>
+        </is>
+      </c>
+      <c r="R32" s="9" t="inlineStr"/>
       <c r="S32" s="9" t="inlineStr"/>
-      <c r="T32" s="9" t="inlineStr">
-        <is>
-          <t>SR21</t>
-        </is>
-      </c>
+      <c r="T32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>E2a-01</t>
+          <t>E2-02</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Collection Rate: collected receivables payments over receivables payments due for the period, excluding deposits</t>
+          <t>Collection Rate and other substitute metrics must not be used in place of the Repayment Rate calculation; the only accepted alternative basis is cumulative arrears</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>rule</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -3584,47 +3584,47 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>CGAP, GOGLA, IFC Lighting Global</t>
+          <t>GOGLA (PAYGo PERFORM initiative)</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>July 2021</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>18-19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>Portfolio Quality Indicators, 1.3 Collection Rate</t>
+          <t>Repayment Rate: Core Calculation Rules, rule 3A and 3B</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+          <t>Project file (uploaded 3 Oct 2026)</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>Industry standard (superseded), read in the project file</t>
+          <t>Industry standard, read in the project file</t>
         </is>
       </c>
       <c r="N33" s="9" t="inlineStr">
@@ -3634,17 +3634,17 @@
       </c>
       <c r="O33" s="9" t="inlineStr">
         <is>
-          <t>VERIFIED (HISTORICAL)</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>Ch 7.2</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="Q33" s="9" t="inlineStr">
         <is>
-          <t>KPIs (operational collection rate), Covenants</t>
+          <t>KPIs labels (change M3)</t>
         </is>
       </c>
       <c r="R33" s="9" t="inlineStr"/>
@@ -3654,17 +3654,17 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>E2a-02</t>
+          <t>E2-03</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Receivables at Risk by consecutive days unpaid, RAR(CDU): gross outstanding receivables more than X consecutive days unpaid over gross outstanding receivables; suggested ageing RAR30, 90, 120, 180, 365</t>
+          <t>Repayment Rate rules: excludes deposits and prepayments; includes arrears payments and write-offs; cumulative since contract start after any free-use period; instalments normalised to daily equivalents; payments recognised pro rata when applied to due instalments</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>rules</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -3674,47 +3674,47 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>CGAP, GOGLA, IFC Lighting Global</t>
+          <t>GOGLA (PAYGo PERFORM initiative)</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>July 2021</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>21-23</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>1.4a Receivables at Risk using Consecutive Days Unpaid</t>
+          <t>Repayment Rate: Definition, Formula; Core Calculation Rules</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+          <t>Project file (uploaded 3 Oct 2026)</t>
         </is>
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>Industry standard (superseded), read in the project file</t>
+          <t>Industry standard, read in the project file</t>
         </is>
       </c>
       <c r="N34" s="9" t="inlineStr">
@@ -3724,17 +3724,17 @@
       </c>
       <c r="O34" s="9" t="inlineStr">
         <is>
-          <t>VERIFIED (HISTORICAL)</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P34" s="9" t="inlineStr">
         <is>
-          <t>Ch 7.2</t>
+          <t>Ch 6, 7</t>
         </is>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
-          <t>KPIs (model RaR is a curve-based proxy, not this definition)</t>
+          <t>Planned PERFORM 2026 block (change M3)</t>
         </is>
       </c>
       <c r="R34" s="9" t="inlineStr"/>
@@ -3744,12 +3744,12 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>E2a-03</t>
+          <t>E2-04</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Receivables at Risk by collection-rate threshold: gross outstanding receivables of customers with collection rate below Y%</t>
+          <t>Ownership Rate @2x: proportion of contracts fully paid as of twice the contract term, among contracts that have reached at least 2x</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -3764,47 +3764,47 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+          <t>PAYGo PERFORM KPIs: Industry Standards for End-User Asset Financing, Technical Guide</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>CGAP, GOGLA, IFC Lighting Global</t>
+          <t>GOGLA (PAYGo PERFORM initiative)</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>July 2021</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+          <t>617b6faf-PAYGo-PERFORM-KPIs_Technical-Guide_2026.pdf (42 pages)</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8; 16-18</t>
         </is>
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>1.4b</t>
+          <t>Ownership Rate</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+          <t>Project file (uploaded 3 Oct 2026)</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>Industry standard (superseded), read in the project file</t>
+          <t>Industry standard, read in the project file</t>
         </is>
       </c>
       <c r="N35" s="9" t="inlineStr">
@@ -3814,17 +3814,17 @@
       </c>
       <c r="O35" s="9" t="inlineStr">
         <is>
-          <t>VERIFIED (HISTORICAL)</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P35" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ch 7, 13</t>
         </is>
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Vintage_Dashboard, RBF_Engine (ownership-linked RBF)</t>
         </is>
       </c>
       <c r="R35" s="9" t="inlineStr"/>
@@ -3834,17 +3834,17 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>E2a-04</t>
+          <t>E2-05</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Write-off Ratio: outstanding receivables of contracts written off in the period over average outstanding receivables</t>
+          <t>At a Glance companion: core RR calculation rules (1) exclude deposits (2) exclude prepayments (3) include arrears payments (4) include write-offs (5) cumulative since contract start</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>definition</t>
+          <t>rules</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -3854,47 +3854,43 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+          <t>PAYGo PERFORM KPIs, At a Glance</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>CGAP, GOGLA, IFC Lighting Global</t>
+          <t>GOGLA (PAYGo PERFORM initiative)</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>July 2021</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+          <t>70d4c519-PAYGo-PERFORM-KPIs_At-A-Glance_2026.pdf (12 pages)</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>Write-off Ratio</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr"/>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+          <t>Project file (uploaded 3 Oct 2026)</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>Industry standard (superseded), read in the project file</t>
+          <t>Industry standard, read in the project file</t>
         </is>
       </c>
       <c r="N36" s="9" t="inlineStr">
@@ -3904,17 +3900,17 @@
       </c>
       <c r="O36" s="9" t="inlineStr">
         <is>
-          <t>VERIFIED (HISTORICAL)</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P36" s="9" t="inlineStr">
         <is>
-          <t>Ch 7.2</t>
+          <t>Ch 7</t>
         </is>
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>KPIs write-off rate (model definition differs: missed instalments written off as due)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="R36" s="9" t="inlineStr"/>
@@ -3924,17 +3920,17 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>E2b-01</t>
+          <t>E2-06</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>PAYGo Accounting Brief: revenue recognition (IFRS 15), write-off and provisioning (IFRS 9) practice for PAYGo</t>
+          <t>PAYGo PERFORM framework attributed to CGAP, GOGLA and Lighting Global with collection rate and receivables at risk as framework KPIs</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>framework</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -3949,42 +3945,38 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>PAYGo Accounting Brief</t>
+          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM initiative (CGAP, GOGLA, IFC Lighting Global); authored by MFR</t>
+          <t>CGAP, GOGLA, IFC Lighting Global</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>October 2021</t>
+          <t>July 2021</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>7d89d499-PAYGo-PERFORM-Accounting-Brief.pdf (67 pages)</t>
+          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>Revenue recognition; Write-off and provisioning policy</t>
-        </is>
-      </c>
+          <t>Front matter</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>Project file</t>
+          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>Practitioner guidance, held; not an accounting standard</t>
+          <t>Industry standard (superseded), read in the project file</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
@@ -3994,37 +3986,45 @@
       </c>
       <c r="O37" s="10" t="inlineStr">
         <is>
-          <t>NOT USED</t>
+          <t>VERIFIED (HISTORICAL)</t>
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>Planned: Ch 8 (context only)</t>
+          <t>Ch 7.1</t>
         </is>
       </c>
       <c r="Q37" s="10" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R37" s="10" t="inlineStr"/>
+          <t>Previous register entry (SR21) replaced by E2-01 to E2-05 and E2a</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>The 2021 framing is historical; the current standard is E2 (June 2026).</t>
+        </is>
+      </c>
       <c r="S37" s="10" t="inlineStr"/>
-      <c r="T37" s="10" t="inlineStr"/>
+      <c r="T37" s="10" t="inlineStr">
+        <is>
+          <t>SR21</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>E2c-01</t>
+          <t>E2a-01</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Guidance for Company Analysis, v3 Beta</t>
+          <t>Collection Rate: collected receivables payments over receivables payments due for the period, excluding deposits</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>definition</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -4034,43 +4034,47 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>PAYGo PERFORM: Guidance for Company Analysis, v3 Beta</t>
+          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>GOGLA (PAYGo PERFORM)</t>
+          <t>CGAP, GOGLA, IFC Lighting Global</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>July 2025</t>
+          <t>July 2021</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>bb716947-PAYGo-PERFORM_Guidance-for-Company-Analysis_v3-beta.pdf (63 pages)</t>
+          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr"/>
+          <t>18-19</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio Quality Indicators, 1.3 Collection Rate</t>
+        </is>
+      </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>Project file</t>
+          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>Beta guidance, held</t>
+          <t>Industry standard (superseded), read in the project file</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
@@ -4080,17 +4084,17 @@
       </c>
       <c r="O38" s="10" t="inlineStr">
         <is>
-          <t>NOT USED</t>
+          <t>VERIFIED (HISTORICAL)</t>
         </is>
       </c>
       <c r="P38" s="10" t="inlineStr">
         <is>
-          <t>Planned: Ch 15 (beta status to be stated)</t>
+          <t>Ch 7.2</t>
         </is>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>KPIs (operational collection rate), Covenants</t>
         </is>
       </c>
       <c r="R38" s="10" t="inlineStr"/>
@@ -4100,499 +4104,493 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>E2d-01</t>
+          <t>E2a-02</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Guidance for PAYGo RBF Funds: metrics and incentives for sustained energy access</t>
+          <t>Receivables at Risk by consecutive days unpaid, RAR(CDU): gross outstanding receivables more than X consecutive days unpaid over gross outstanding receivables; suggested ageing RAR30, 90, 120, 180, 365</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>CGAP, GOGLA, IFC Lighting Global</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>July 2021</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>21-23</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>1.4a Receivables at Risk using Consecutive Days Unpaid</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>Industry standard (superseded), read in the project file</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O39" s="10" t="inlineStr">
+        <is>
+          <t>VERIFIED (HISTORICAL)</t>
+        </is>
+      </c>
+      <c r="P39" s="10" t="inlineStr">
+        <is>
+          <t>Ch 7.2</t>
+        </is>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>KPIs (model RaR is a curve-based proxy, not this definition)</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="inlineStr"/>
+      <c r="S39" s="10" t="inlineStr"/>
+      <c r="T39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>E2a-03</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Receivables at Risk by collection-rate threshold: gross outstanding receivables of customers with collection rate below Y%</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>CGAP, GOGLA, IFC Lighting Global</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>July 2021</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>1.4b</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>Industry standard (superseded), read in the project file</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O40" s="10" t="inlineStr">
+        <is>
+          <t>VERIFIED (HISTORICAL)</t>
+        </is>
+      </c>
+      <c r="P40" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="inlineStr"/>
+      <c r="S40" s="10" t="inlineStr"/>
+      <c r="T40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>E2a-04</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Write-off Ratio: outstanding receivables of contracts written off in the period over average outstanding receivables</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>PAYGo PERFORM Technical Guide: Financial, Operational, and Portfolio Quality KPIs for the PAYGo solar industry</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>CGAP, GOGLA, IFC Lighting Global</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>July 2021</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>a30c1991-2021_07_Technical_Guide_PAYGo_PERFORM_KPI.pdf (85 pages)</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Write-off Ratio</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026; a byte-identical second copy was also uploaded)</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Industry standard (superseded), read in the project file</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O41" s="10" t="inlineStr">
+        <is>
+          <t>VERIFIED (HISTORICAL)</t>
+        </is>
+      </c>
+      <c r="P41" s="10" t="inlineStr">
+        <is>
+          <t>Ch 7.2</t>
+        </is>
+      </c>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>KPIs write-off rate (model definition differs: missed instalments written off as due)</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="inlineStr"/>
+      <c r="S41" s="10" t="inlineStr"/>
+      <c r="T41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>E2b-01</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>PAYGo Accounting Brief: revenue recognition (IFRS 15), write-off and provisioning (IFRS 9) practice for PAYGo</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>Guidance for PAYGo RBF Funds</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>PAYGo PERFORM initiative</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>April 2026</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>833f21cf-Guidance-for-PAYGo-RBFs-Metrics-Incentives-for-Sustained-Energy-Access.pdf (27 pages)</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>PAYGo Accounting Brief</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>PAYGo PERFORM initiative (CGAP, GOGLA, IFC Lighting Global); authored by MFR</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>October 2021</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>7d89d499-PAYGo-PERFORM-Accounting-Brief.pdf (67 pages)</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>Revenue recognition; Write-off and provisioning policy</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr">
         <is>
           <t>Project file</t>
         </is>
       </c>
-      <c r="M39" s="10" t="inlineStr">
-        <is>
-          <t>Institutional guidance, held</t>
-        </is>
-      </c>
-      <c r="N39" s="10" t="inlineStr">
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>Practitioner guidance, held; not an accounting standard</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O39" s="10" t="inlineStr">
+      <c r="O42" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
-      <c r="P39" s="10" t="inlineStr">
-        <is>
-          <t>Planned: Ch 13</t>
-        </is>
-      </c>
-      <c r="Q39" s="10" t="inlineStr">
-        <is>
-          <t>Planned: RBF_Engine review (change M11)</t>
-        </is>
-      </c>
-      <c r="R39" s="10" t="inlineStr">
-        <is>
-          <t>Replaces the SR22 list item for this document. The other GOGLA publications listed in SR22 are not held.</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr"/>
-      <c r="T39" s="10" t="inlineStr">
-        <is>
-          <t>SR22</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>E3-01</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Multi-Tier Framework capacity thresholds (T4 at least 800 W / 3.4 kWh a day; T5 at least 2 kW / 8.2 kWh a day)</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>T1-T5</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>Planned: Ch 8 (context only)</t>
+        </is>
+      </c>
+      <c r="Q42" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R42" s="11" t="inlineStr"/>
+      <c r="S42" s="11" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>E2c-01</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Guidance for Company Analysis, v3 Beta</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>Beyond Connections: Energy Access Redefined</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>ESMAP / World Bank</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Not held</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>PAYGo PERFORM: Guidance for Company Analysis, v3 Beta</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>GOGLA (PAYGo PERFORM)</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>July 2025</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>bb716947-PAYGo-PERFORM_Guidance-for-Company-Analysis_v3-beta.pdf (63 pages)</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>Thresholds recorded from earlier research; framework report not read</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>Project file</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>Beta guidance, held</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O40" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P40" s="7" t="inlineStr">
-        <is>
-          <t>Ch 2.6</t>
-        </is>
-      </c>
-      <c r="Q40" s="7" t="inlineStr">
-        <is>
-          <t>Products tier labels</t>
-        </is>
-      </c>
-      <c r="R40" s="7" t="inlineStr"/>
-      <c r="S40" s="7" t="inlineStr"/>
-      <c r="T40" s="7" t="inlineStr">
-        <is>
-          <t>SR20</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>E4-01</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>M-KOPA UK LIMITED revenue (sales of carbon credits)</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>1712776</v>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>FY2024 (FY2023: 718,100)</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>Companies House (company 10229661)</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>10 (filing page 8); 18 (filing page 16, note 2.1)</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>Statement of profit or loss; note 2.1 Sale of carbon credits</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t>Planned: Ch 15 (as an illustration of entity checking)</t>
-        </is>
-      </c>
-      <c r="Q41" s="8" t="inlineStr">
-        <is>
-          <t>Not used: different entity and activity; not a PAYGo benchmark</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t>UK research and development subsidiary; no employees; functional currency sterling; IFRS as adopted in the UK; not consolidated.</t>
-        </is>
-      </c>
-      <c r="S41" s="8" t="inlineStr"/>
-      <c r="T41" s="8" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>E4-02</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>M-KOPA UK LIMITED profit for the year</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>1040472</v>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>FY2024 (FY2023: 497,346)</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>Companies House (company 10229661)</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
-        </is>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>10 (filing page 8)</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>Statement of profit or loss</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O42" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="P42" s="8" t="inlineStr">
+      <c r="O43" s="11" t="inlineStr">
+        <is>
+          <t>NOT USED</t>
+        </is>
+      </c>
+      <c r="P43" s="11" t="inlineStr">
+        <is>
+          <t>Planned: Ch 15 (beta status to be stated)</t>
+        </is>
+      </c>
+      <c r="Q43" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q42" s="8" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="R42" s="8" t="inlineStr"/>
-      <c r="S42" s="8" t="inlineStr"/>
-      <c r="T42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>E4-03</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>M-KOPA UK LIMITED parent and ultimate parent: M-Kopa LLC (Delaware); M-Kopa Holdings Limited (London)</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>Companies House (company 10229661)</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>3 (filing page 1)</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>Company information</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O43" s="8" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="P43" s="8" t="inlineStr">
-        <is>
-          <t>Planned: Ch 15</t>
-        </is>
-      </c>
-      <c r="Q43" s="8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R43" s="8" t="inlineStr">
-        <is>
-          <t>The project's benchmark files attribute the group figures to M-KOPA Holdings Ltd, Companies House 10891868. That number has not been checked against the register.</t>
-        </is>
-      </c>
-      <c r="S43" s="8" t="inlineStr"/>
-      <c r="T43" s="8" t="inlineStr"/>
+      <c r="R43" s="11" t="inlineStr"/>
+      <c r="S43" s="11" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>E4-04</t>
+          <t>E2d-01</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>M-KOPA group revenue FY2024</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>416</v>
+          <t>Guidance for PAYGo RBF Funds: metrics and incentives for sustained energy access</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>News article citing 'UK filings'</t>
+          <t>Guidance for PAYGo RBF Funds</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>TechCabal</t>
+          <t>PAYGo PERFORM initiative</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>7 Oct 2025</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>833f21cf-Guidance-for-PAYGo-RBFs-Metrics-Incentives-for-Sustained-Energy-Access.pdf (27 pages)</t>
         </is>
       </c>
       <c r="J44" s="11" t="inlineStr">
@@ -4603,634 +4601,628 @@
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="inlineStr">
         <is>
+          <t>Project file</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>Institutional guidance, held</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="inlineStr">
+        <is>
+          <t>NOT USED</t>
+        </is>
+      </c>
+      <c r="P44" s="11" t="inlineStr">
+        <is>
+          <t>Planned: Ch 13</t>
+        </is>
+      </c>
+      <c r="Q44" s="11" t="inlineStr">
+        <is>
+          <t>Planned: RBF_Engine review (change M11)</t>
+        </is>
+      </c>
+      <c r="R44" s="11" t="inlineStr">
+        <is>
+          <t>Replaces the SR22 list item for this document. The other GOGLA publications listed in SR22 are not held.</t>
+        </is>
+      </c>
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr">
+        <is>
+          <t>SR22</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>E3-01</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Tier Framework capacity thresholds (T4 at least 800 W / 3.4 kWh a day; T5 at least 2 kW / 8.2 kWh a day)</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>T1-T5</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Beyond Connections: Energy Access Redefined</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>ESMAP / World Bank</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Not held</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>Thresholds recorded from earlier research; framework report not read</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>Ch 2.6</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>Products tier labels</t>
+        </is>
+      </c>
+      <c r="R45" s="7" t="inlineStr"/>
+      <c r="S45" s="7" t="inlineStr"/>
+      <c r="T45" s="7" t="inlineStr">
+        <is>
+          <t>SR20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>E4-01</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED revenue (sales of carbon credits)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>1712776</v>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>FY2024 (FY2023: 718,100)</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Companies House (company 10229661)</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>10 (filing page 8); 18 (filing page 16, note 2.1)</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>Statement of profit or loss; note 2.1 Sale of carbon credits</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
+        </is>
+      </c>
+      <c r="N46" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="inlineStr">
+        <is>
+          <t>Planned: Ch 15 (as an illustration of entity checking)</t>
+        </is>
+      </c>
+      <c r="Q46" s="9" t="inlineStr">
+        <is>
+          <t>Not used: different entity and activity; not a PAYGo benchmark</t>
+        </is>
+      </c>
+      <c r="R46" s="9" t="inlineStr">
+        <is>
+          <t>UK research and development subsidiary; no employees; functional currency sterling; IFRS as adopted in the UK; not consolidated.</t>
+        </is>
+      </c>
+      <c r="S46" s="9" t="inlineStr"/>
+      <c r="T46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>E4-02</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED profit for the year</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>1040472</v>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>FY2024 (FY2023: 497,346)</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Companies House (company 10229661)</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>10 (filing page 8)</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>Statement of profit or loss</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
+        </is>
+      </c>
+      <c r="N47" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O47" s="9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P47" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q47" s="9" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+      <c r="R47" s="9" t="inlineStr"/>
+      <c r="S47" s="9" t="inlineStr"/>
+      <c r="T47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>E4-03</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED parent and ultimate parent: M-Kopa LLC (Delaware); M-Kopa Holdings Limited (London)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Companies House (company 10229661)</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>3 (filing page 1)</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>Company information</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
+        </is>
+      </c>
+      <c r="N48" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="inlineStr">
+        <is>
+          <t>Planned: Ch 15</t>
+        </is>
+      </c>
+      <c r="Q48" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R48" s="9" t="inlineStr">
+        <is>
+          <t>The project's benchmark files attribute the group figures to M-KOPA Holdings Ltd, Companies House 10891868. That number has not been checked against the register.</t>
+        </is>
+      </c>
+      <c r="S48" s="9" t="inlineStr"/>
+      <c r="T48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>E4-04</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>M-KOPA group revenue FY2024</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>416</v>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>News article citing 'UK filings'</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>TechCabal</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>7 Oct 2025</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Web article</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr"/>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
           <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
         </is>
       </c>
-      <c r="M44" s="11" t="inlineStr">
+      <c r="M49" s="8" t="inlineStr">
         <is>
           <t>Secondary report; entity and revenue line not identified</t>
         </is>
       </c>
-      <c r="N44" s="11" t="inlineStr">
+      <c r="N49" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O44" s="11" t="inlineStr">
+      <c r="O49" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
       </c>
-      <c r="P44" s="11" t="inlineStr">
+      <c r="P49" s="8" t="inlineStr">
         <is>
           <t>Ch 15 (presented as conflicting)</t>
         </is>
       </c>
-      <c r="Q44" s="11" t="inlineStr">
+      <c r="Q49" s="8" t="inlineStr">
         <is>
           <t>Market_Benchmark and Calibration: suspended</t>
         </is>
       </c>
-      <c r="R44" s="11" t="inlineStr">
+      <c r="R49" s="8" t="inlineStr">
         <is>
           <t>Conflicts with E4-05 (USD 253.5m). Not supported by E4-01 (different entity). Resolvable only with the consolidated accounts of the reporting group entity.</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="S49" s="8" t="inlineStr">
         <is>
           <t>M-KOPA|Revenue</t>
         </is>
       </c>
-      <c r="T44" s="11" t="inlineStr">
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>SR01</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>E4-05</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>M-KOPA group revenue FY2024</t>
         </is>
       </c>
-      <c r="C45" s="11" t="n">
+      <c r="C50" s="8" t="n">
         <v>253.5</v>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>News article</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Kenyan Wall Street</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>Web article</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr"/>
-      <c r="L45" s="11" t="inlineStr">
+      <c r="K50" s="8" t="inlineStr"/>
+      <c r="L50" s="8" t="inlineStr">
         <is>
           <t>https://kenyanwallstreet.com/m-kopa-posts-first-ever-profit-bets-on-e-mobility-for-next-growth-phase/</t>
         </is>
       </c>
-      <c r="M45" s="11" t="inlineStr">
+      <c r="M50" s="8" t="inlineStr">
         <is>
           <t>Secondary report; may be a different revenue line</t>
         </is>
       </c>
-      <c r="N45" s="11" t="inlineStr">
+      <c r="N50" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O45" s="11" t="inlineStr">
+      <c r="O50" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
       </c>
-      <c r="P45" s="11" t="inlineStr">
+      <c r="P50" s="8" t="inlineStr">
         <is>
           <t>Ch 15 (presented as conflicting)</t>
         </is>
       </c>
-      <c r="Q45" s="11" t="inlineStr">
+      <c r="Q50" s="8" t="inlineStr">
         <is>
           <t>Not used</t>
         </is>
       </c>
-      <c r="R45" s="11" t="inlineStr"/>
-      <c r="S45" s="11" t="inlineStr"/>
-      <c r="T45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>E4-06</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>M-KOPA group revenue growth</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>FY2024 vs FY2023</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>News articles</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>TechCabal; Kenyan Wall Street</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Web articles</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
-        </is>
-      </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>Secondary report</t>
-        </is>
-      </c>
-      <c r="N46" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O46" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P46" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q46" s="7" t="inlineStr">
-        <is>
-          <t>Calibration growth reference: suspended</t>
-        </is>
-      </c>
-      <c r="R46" s="7" t="inlineStr"/>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>M-KOPA|Revenue growth</t>
-        </is>
-      </c>
-      <c r="T46" s="7" t="inlineStr">
-        <is>
-          <t>SR02</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>E4-07</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>M-KOPA group net profit</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>USD m</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>News article</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>TechCabal</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>7 Oct 2025</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Web article</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>Secondary report</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O47" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>Ch 15</t>
-        </is>
-      </c>
-      <c r="Q47" s="7" t="inlineStr">
-        <is>
-          <t>Calibration net margin reference: suspended</t>
-        </is>
-      </c>
-      <c r="R47" s="7" t="inlineStr"/>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>M-KOPA|Net profit</t>
-        </is>
-      </c>
-      <c r="T47" s="7" t="inlineStr">
-        <is>
-          <t>SR03</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>E4-08</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>M-KOPA group net result, prior year</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>-24.7 (or -20.6)</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>USD m</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>News articles</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>TechCabal; Kenyan Wall Street</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>Web articles</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K48" s="11" t="inlineStr"/>
-      <c r="L48" s="11" t="inlineStr">
-        <is>
-          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
-        </is>
-      </c>
-      <c r="M48" s="11" t="inlineStr">
-        <is>
-          <t>Secondary reports that conflict</t>
-        </is>
-      </c>
-      <c r="N48" s="11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O48" s="11" t="inlineStr">
-        <is>
-          <t>CONFLICTING SOURCES</t>
-        </is>
-      </c>
-      <c r="P48" s="11" t="inlineStr">
-        <is>
-          <t>Ch 15</t>
-        </is>
-      </c>
-      <c r="Q48" s="11" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="R48" s="11" t="inlineStr"/>
-      <c r="S48" s="11" t="inlineStr"/>
-      <c r="T48" s="11" t="inlineStr">
-        <is>
-          <t>SR04</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>E5-01</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Sun King cumulative solar loans</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>USD m</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>Cumulative to Jul 2025</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Citi press release on the Sun King securitisation</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>Citigroup</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>Press release (not read in this project)</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>Company disclosure recorded from earlier research</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="O49" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P49" s="7" t="inlineStr">
-        <is>
-          <t>Ch 12, 15</t>
-        </is>
-      </c>
-      <c r="Q49" s="7" t="inlineStr">
-        <is>
-          <t>Market_Benchmark (shown, flagged)</t>
-        </is>
-      </c>
-      <c r="R49" s="7" t="inlineStr"/>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>Sun King|Cumulative solar loans</t>
-        </is>
-      </c>
-      <c r="T49" s="7" t="inlineStr">
-        <is>
-          <t>SR05</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>E5-02</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Sun King cumulative loan customers (cumulative, not active)</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>million</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>Cumulative to Jul 2025</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Citi press release</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>Citigroup</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>Press release (not read)</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
-        </is>
-      </c>
-      <c r="M50" s="7" t="inlineStr">
-        <is>
-          <t>Company disclosure recorded from earlier research</t>
-        </is>
-      </c>
-      <c r="N50" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="O50" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P50" s="7" t="inlineStr">
-        <is>
-          <t>Ch 12, 15</t>
-        </is>
-      </c>
-      <c r="Q50" s="7" t="inlineStr">
-        <is>
-          <t>Market_Benchmark (shown, flagged)</t>
-        </is>
-      </c>
-      <c r="R50" s="7" t="inlineStr"/>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>Sun King|Cumulative loan customers</t>
-        </is>
-      </c>
-      <c r="T50" s="7" t="inlineStr">
-        <is>
-          <t>SR06</t>
-        </is>
-      </c>
+      <c r="R50" s="8" t="inlineStr"/>
+      <c r="S50" s="8" t="inlineStr"/>
+      <c r="T50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>E5-03</t>
+          <t>E4-06</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Sun King local-currency securitisation in Kenya</t>
+          <t>M-KOPA group revenue growth</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>130</v>
+        <v>0.66</v>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>FY2024 vs FY2023</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Sun King news release</t>
+          <t>News articles</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Sun King</t>
+          <t>TechCabal; Kenyan Wall Street</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Oct 2025</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>News release (not read)</t>
+          <t>Web articles</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -5241,17 +5233,17 @@
       <c r="K51" s="7" t="inlineStr"/>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>https://sunking.com/news-blog/sun-king-and-citi-close-first-130-million-securitisation-to-broaden-access-to-finance-for-off-grid-solar-in-kenya/</t>
+          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>Company disclosure recorded from earlier research</t>
+          <t>Secondary report</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
@@ -5261,35 +5253,39 @@
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
-          <t>Ch 3.11, 11, 12</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Calibration growth reference: suspended</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr"/>
-      <c r="S51" s="7" t="inlineStr"/>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>M-KOPA|Revenue growth</t>
+        </is>
+      </c>
       <c r="T51" s="7" t="inlineStr">
         <is>
-          <t>SR07</t>
+          <t>SR02</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>E5-04</t>
+          <t>E4-07</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Sun King local-currency securitisation in Kenya (KES 20.1bn)</t>
+          <t>M-KOPA group net profit</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>156</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
@@ -5298,27 +5294,27 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Jul 2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Citi release; trade press</t>
+          <t>News article</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Citigroup; pv magazine</t>
+          <t>TechCabal</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>29 Jul 2025</t>
+          <t>7 Oct 2025</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Release and article (not read)</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
@@ -5329,17 +5325,17 @@
       <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2025/07/29/sun-king-closes-156m-off-grid-solar-deal-in-kenya/</t>
+          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>Company disclosure and secondary report recorded from earlier research</t>
+          <t>Secondary report</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O52" s="7" t="inlineStr">
@@ -5349,107 +5345,129 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>Ch 3.11, 11, 12</t>
+          <t>Ch 15</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
-          <t>Market_Benchmark (shown, flagged)</t>
+          <t>Calibration net margin reference: suspended</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr"/>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>Sun King|Securitisation 2025</t>
+          <t>M-KOPA|Net profit</t>
         </is>
       </c>
       <c r="T52" s="7" t="inlineStr">
         <is>
-          <t>SR08</t>
+          <t>SR03</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>E5-05</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Sun King MSME bond</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>E4-08</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>M-KOPA group net result, prior year</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>-24.7 (or -20.6)</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr"/>
-      <c r="H53" s="10" t="inlineStr"/>
-      <c r="I53" s="10" t="inlineStr"/>
-      <c r="J53" s="10" t="inlineStr"/>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr">
-        <is>
-          <t>No public source found</t>
-        </is>
-      </c>
-      <c r="N53" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="O53" s="10" t="inlineStr">
-        <is>
-          <t>NOT USED</t>
-        </is>
-      </c>
-      <c r="P53" s="10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q53" s="10" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="R53" s="10" t="inlineStr"/>
-      <c r="S53" s="10" t="inlineStr"/>
-      <c r="T53" s="10" t="inlineStr">
-        <is>
-          <t>SR09</t>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>News articles</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>TechCabal; Kenyan Wall Street</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>Web articles</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr"/>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="inlineStr">
+        <is>
+          <t>Secondary reports that conflict</t>
+        </is>
+      </c>
+      <c r="N53" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>CONFLICTING SOURCES</t>
+        </is>
+      </c>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>Ch 15</t>
+        </is>
+      </c>
+      <c r="Q53" s="8" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+      <c r="R53" s="8" t="inlineStr"/>
+      <c r="S53" s="8" t="inlineStr"/>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>SR04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>E6-01</t>
+          <t>E5-01</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>d.light securitisation purchasing capacity since 2020 (five facilities; purchasing capacity, not debt raised)</t>
+          <t>Sun King cumulative solar loans</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>718</v>
+        <v>1300</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
@@ -5458,27 +5476,27 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>2020 to Jul 2024</t>
+          <t>Cumulative to Jul 2025</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>News article</t>
+          <t>Citi press release on the Sun King securitisation</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Techpoint Africa</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>17 Jul 2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Press release (not read in this project)</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
@@ -5489,17 +5507,17 @@
       <c r="K54" s="7" t="inlineStr"/>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
+          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>Secondary report</t>
+          <t>Company disclosure recorded from earlier research</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
@@ -5509,7 +5527,7 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>Ch 3.11, 11, 12, 15</t>
+          <t>Ch 12, 15</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
@@ -5520,57 +5538,57 @@
       <c r="R54" s="7" t="inlineStr"/>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>d.light|Securitisation purchasing capacity since 2020</t>
+          <t>Sun King|Cumulative solar loans</t>
         </is>
       </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
-          <t>SR10</t>
+          <t>SR05</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>E6-02</t>
+          <t>E5-02</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>d.light multi-currency securitisation facility</t>
+          <t>Sun King cumulative loan customers (cumulative, not active)</t>
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>176</v>
+        <v>10</v>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>million</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Jul 2024</t>
+          <t>Cumulative to Jul 2025</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>News articles</t>
+          <t>Citi press release</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Techpoint Africa; WeeTracker</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>17 Jul 2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Web articles</t>
+          <t>Press release (not read)</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
@@ -5581,17 +5599,17 @@
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
+          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>Secondary report</t>
+          <t>Company disclosure recorded from earlier research</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
@@ -5601,7 +5619,7 @@
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>Ch 12</t>
+          <t>Ch 12, 15</t>
         </is>
       </c>
       <c r="Q55" s="7" t="inlineStr">
@@ -5612,57 +5630,57 @@
       <c r="R55" s="7" t="inlineStr"/>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>d.light|Securitisation facility 2024</t>
+          <t>Sun King|Cumulative loan customers</t>
         </is>
       </c>
       <c r="T55" s="7" t="inlineStr">
         <is>
-          <t>SR11</t>
+          <t>SR06</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>E6-03</t>
+          <t>E5-03</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>d.light revenue growth</t>
+          <t>Sun King local-currency securitisation in Kenya</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>0.41</v>
+        <v>130</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>H1 2023 vs H1 2022</t>
+          <t>May 2023</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>d.light press release</t>
+          <t>Sun King news release</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>d.light via PR Newswire</t>
+          <t>Sun King</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Press release (not read)</t>
+          <t>News release (not read)</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
@@ -5673,7 +5691,7 @@
       <c r="K56" s="7" t="inlineStr"/>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.co.uk/news-releases/dlight-revenues-surge-by-41-percent-in-first-six-months-of-2023-driven-by-143-percent-growth-in-nigeria-301919233.html</t>
+          <t>https://sunking.com/news-blog/sun-king-and-citi-close-first-130-million-securitisation-to-broaden-access-to-finance-for-off-grid-solar-in-kenya/</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -5693,265 +5711,245 @@
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
+          <t>Ch 3.11, 11, 12</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q56" s="7" t="inlineStr">
+      <c r="R56" s="7" t="inlineStr"/>
+      <c r="S56" s="7" t="inlineStr"/>
+      <c r="T56" s="7" t="inlineStr">
+        <is>
+          <t>SR07</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>E5-04</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Sun King local-currency securitisation in Kenya (KES 20.1bn)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Citi release; trade press</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Citigroup; pv magazine</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>29 Jul 2025</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Release and article (not read)</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2025/07/29/sun-king-closes-156m-off-grid-solar-deal-in-kenya/</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>Company disclosure and secondary report recorded from earlier research</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O57" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>Ch 3.11, 11, 12</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
         <is>
           <t>Market_Benchmark (shown, flagged)</t>
         </is>
       </c>
-      <c r="R56" s="7" t="inlineStr"/>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>d.light|Revenue growth</t>
-        </is>
-      </c>
-      <c r="T56" s="7" t="inlineStr">
-        <is>
-          <t>SR12</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>E6-04</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>d.light revenue (third-party estimate)</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>301.2</v>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="R57" s="7" t="inlineStr"/>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>Sun King|Securitisation 2025</t>
+        </is>
+      </c>
+      <c r="T57" s="7" t="inlineStr">
+        <is>
+          <t>SR08</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>E5-05</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Sun King MSME bond</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>Company database</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>bitscale.ai</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>Web page</t>
-        </is>
-      </c>
-      <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr">
-        <is>
-          <t>https://www.bitscale.ai/directory/dlight</t>
-        </is>
-      </c>
-      <c r="M57" s="10" t="inlineStr">
-        <is>
-          <t>Third-party estimate, method not stated</t>
-        </is>
-      </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr"/>
+      <c r="I58" s="11" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr"/>
+      <c r="L58" s="11" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>No public source found</t>
+        </is>
+      </c>
+      <c r="N58" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="O57" s="10" t="inlineStr">
+      <c r="O58" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
-      <c r="P57" s="10" t="inlineStr">
+      <c r="P58" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q57" s="10" t="inlineStr">
+      <c r="Q58" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="R57" s="10" t="inlineStr"/>
-      <c r="S57" s="10" t="inlineStr"/>
-      <c r="T57" s="10" t="inlineStr">
-        <is>
-          <t>SR13</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>E7-01</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>BBOXX LTD (07177839): appointment of administrators</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>19 May 2025</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>Notice of appointment of administrators</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>The Gazette</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>2025 (to verify)</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>Gazette notice 4891954 (not held)</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr">
-        <is>
-          <t>Notice</t>
-        </is>
-      </c>
-      <c r="K58" s="7" t="inlineStr"/>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>https://www.thegazette.co.uk/notice/4891954 (not opened from this environment)</t>
-        </is>
-      </c>
-      <c r="M58" s="7" t="inlineStr">
-        <is>
-          <t>Date recorded from earlier research (Gazette and administrator's announcement); notice not read in this project</t>
-        </is>
-      </c>
-      <c r="N58" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O58" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P58" s="7" t="inlineStr">
-        <is>
-          <t>Ch 1.6, 14</t>
-        </is>
-      </c>
-      <c r="Q58" s="7" t="inlineStr">
-        <is>
-          <t>Company_Cases text</t>
-        </is>
-      </c>
-      <c r="R58" s="7" t="inlineStr">
-        <is>
-          <t>The date must be the date of appointment stated in the formal notice, not a petition, hearing, publication or creditors' meeting date.</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr"/>
-      <c r="T58" s="7" t="inlineStr">
-        <is>
-          <t>SR15</t>
+      <c r="R58" s="11" t="inlineStr"/>
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr">
+        <is>
+          <t>SR09</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>E7-02</t>
+          <t>E6-01</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>BBOXX LTD (07177839): latest filed accounts made up to 31 Dec 2022; FY2023 accounts overdue; status in administration</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
+          <t>d.light securitisation purchasing capacity since 2020 (five facilities; purchasing capacity, not debt raised)</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>718</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>USD m</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020 to Jul 2024</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Companies House register</t>
+          <t>News article</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Companies House</t>
+          <t>Techpoint Africa</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>2025 (to verify)</t>
+          <t>17 Jul 2024</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Register entry (not opened)</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr"/>
+          <t>Web article</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
       <c r="K59" s="7" t="inlineStr"/>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07177839 (not opened from this environment)</t>
+          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>Recorded from earlier research</t>
+          <t>Secondary report</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
@@ -5961,35 +5959,39 @@
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>Ch 1.6</t>
+          <t>Ch 3.11, 11, 12, 15</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
         <is>
-          <t>Company_Cases text</t>
+          <t>Market_Benchmark (shown, flagged)</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr"/>
-      <c r="S59" s="7" t="inlineStr"/>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>d.light|Securitisation purchasing capacity since 2020</t>
+        </is>
+      </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>SR14</t>
+          <t>SR10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>E8-01</t>
+          <t>E6-02</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Off-grid solar investment in 2024, down about 30%</t>
+          <t>d.light multi-currency securitisation facility</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>299</v>
+        <v>176</v>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
@@ -5998,27 +6000,27 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Jul 2024</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>GOGLA investment data (as reported)</t>
+          <t>News articles</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>GOGLA</t>
+          <t>Techpoint Africa; WeeTracker</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>2025 (to verify)</t>
+          <t>17 Jul 2024</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>Not held</t>
+          <t>Web articles</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
@@ -6027,7 +6029,11 @@
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
+        </is>
+      </c>
       <c r="M60" s="7" t="inlineStr">
         <is>
           <t>Secondary report</t>
@@ -6035,7 +6041,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
@@ -6045,64 +6051,68 @@
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>Ch 11.1, 14</t>
+          <t>Ch 12</t>
         </is>
       </c>
       <c r="Q60" s="7" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="R60" s="7" t="inlineStr">
-        <is>
-          <t>Consistency only, not verification: E1-17 gives USD 425m for 2023, and 425 x 0.7 is about 298.</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr"/>
-      <c r="T60" s="7" t="inlineStr"/>
+          <t>Market_Benchmark (shown, flagged)</t>
+        </is>
+      </c>
+      <c r="R60" s="7" t="inlineStr"/>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>d.light|Securitisation facility 2024</t>
+        </is>
+      </c>
+      <c r="T60" s="7" t="inlineStr">
+        <is>
+          <t>SR11</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>E9-01</t>
+          <t>E6-03</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>ZOLA Electric financing round (USD 45m equity, USD 45m debt)</t>
+          <t>d.light revenue growth</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>90</v>
+        <v>0.41</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>H1 2023 vs H1 2022</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>News article</t>
+          <t>d.light press release</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>d.light via PR Newswire</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>23 Sep 2021</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Press release (not read)</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
@@ -6113,17 +6123,17 @@
       <c r="K61" s="7" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2021/09/23/zola-electric-closes-90m-funding-round-to-scale-technology-and-enter-new-markets</t>
+          <t>https://www.prnewswire.co.uk/news-releases/dlight-revenues-surge-by-41-percent-in-first-six-months-of-2023-driven-by-143-percent-growth-in-nigeria-301919233.html</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>Secondary report</t>
+          <t>Company disclosure recorded from earlier research</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -6144,313 +6154,753 @@
       <c r="R61" s="7" t="inlineStr"/>
       <c r="S61" s="7" t="inlineStr">
         <is>
+          <t>d.light|Revenue growth</t>
+        </is>
+      </c>
+      <c r="T61" s="7" t="inlineStr">
+        <is>
+          <t>SR12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>E6-04</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>d.light revenue (third-party estimate)</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>301.2</v>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>Company database</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>bitscale.ai</t>
+        </is>
+      </c>
+      <c r="H62" s="11" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr"/>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>https://www.bitscale.ai/directory/dlight</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>Third-party estimate, method not stated</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O62" s="11" t="inlineStr">
+        <is>
+          <t>NOT USED</t>
+        </is>
+      </c>
+      <c r="P62" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q62" s="11" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="R62" s="11" t="inlineStr"/>
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr">
+        <is>
+          <t>SR13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>E7-01</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>BBOXX LTD (07177839): appointment of administrators</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>19 May 2025</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Notice of appointment of administrators</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>The Gazette</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>2025 (to verify)</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Gazette notice 4891954 (not held)</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>Notice</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr"/>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.thegazette.co.uk/notice/4891954 (not opened from this environment)</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>Date recorded from earlier research (Gazette and administrator's announcement); notice not read in this project</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O63" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>Ch 1.6, 14</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>Company_Cases text</t>
+        </is>
+      </c>
+      <c r="R63" s="7" t="inlineStr">
+        <is>
+          <t>The date must be the date of appointment stated in the formal notice, not a petition, hearing, publication or creditors' meeting date.</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr"/>
+      <c r="T63" s="7" t="inlineStr">
+        <is>
+          <t>SR15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>E7-02</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>BBOXX LTD (07177839): latest filed accounts made up to 31 Dec 2022; FY2023 accounts overdue; status in administration</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Companies House register</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Companies House</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>2025 (to verify)</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>Register entry (not opened)</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07177839 (not opened from this environment)</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>Recorded from earlier research</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>Ch 1.6</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>Company_Cases text</t>
+        </is>
+      </c>
+      <c r="R64" s="7" t="inlineStr"/>
+      <c r="S64" s="7" t="inlineStr"/>
+      <c r="T64" s="7" t="inlineStr">
+        <is>
+          <t>SR14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>E8-01</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Off-grid solar investment in 2024, down about 30%</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>299</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>GOGLA investment data (as reported)</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>GOGLA</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>2025 (to verify)</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Not held</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>Secondary report</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O65" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>Ch 11.1, 14</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R65" s="7" t="inlineStr">
+        <is>
+          <t>Consistency only, not verification: E1-17 gives USD 425m for 2023, and 425 x 0.7 is about 298.</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr"/>
+      <c r="T65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>E9-01</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>ZOLA Electric financing round (USD 45m equity, USD 45m debt)</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2021</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>News article</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>23 Sep 2021</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>Web article</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr"/>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2021/09/23/zola-electric-closes-90m-funding-round-to-scale-technology-and-enter-new-markets</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>Secondary report</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>Market_Benchmark (shown, flagged)</t>
+        </is>
+      </c>
+      <c r="R66" s="7" t="inlineStr"/>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
           <t>ZOLA Electric|Financing round</t>
         </is>
       </c>
-      <c r="T61" s="7" t="inlineStr">
+      <c r="T66" s="7" t="inlineStr">
         <is>
           <t>SR18</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>E10-01</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>SEforALL Universal Energy Facility pays results-based finance per verified connection</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>SEforALL (as reported)</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>SEforALL</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>to verify</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>Not held</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
-      <c r="M62" s="7" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>Secondary description</t>
         </is>
       </c>
-      <c r="N62" s="7" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O62" s="7" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>PENDING PRIMARY DOCUMENT</t>
         </is>
       </c>
-      <c r="P62" s="7" t="inlineStr">
+      <c r="P67" s="7" t="inlineStr">
         <is>
           <t>Ch 13.2</t>
         </is>
       </c>
-      <c r="Q62" s="7" t="inlineStr">
+      <c r="Q67" s="7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R62" s="7" t="inlineStr"/>
-      <c r="S62" s="7" t="inlineStr"/>
-      <c r="T62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="R67" s="7" t="inlineStr"/>
+      <c r="S67" s="7" t="inlineStr"/>
+      <c r="T67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>X-01</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>Pawame SHS financed</t>
         </is>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C68" s="11" t="n">
         <v>18700</v>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr"/>
-      <c r="H63" s="10" t="inlineStr"/>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr"/>
+      <c r="I68" s="11" t="inlineStr"/>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr">
         <is>
           <t>No public source found</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr">
+      <c r="N68" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="O63" s="10" t="inlineStr">
+      <c r="O68" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
-      <c r="P63" s="10" t="inlineStr">
+      <c r="P68" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q63" s="10" t="inlineStr">
+      <c r="Q68" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="R63" s="10" t="inlineStr"/>
-      <c r="S63" s="10" t="inlineStr">
+      <c r="R68" s="11" t="inlineStr"/>
+      <c r="S68" s="11" t="inlineStr">
         <is>
           <t>Pawame|SHS financed</t>
         </is>
       </c>
-      <c r="T63" s="10" t="inlineStr">
+      <c r="T68" s="11" t="inlineStr">
         <is>
           <t>SR16</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>X-02</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>Pawame active customers</t>
         </is>
       </c>
-      <c r="C64" s="10" t="n">
+      <c r="C69" s="11" t="n">
         <v>16000</v>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>customers</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr"/>
-      <c r="H64" s="10" t="inlineStr"/>
-      <c r="I64" s="10" t="inlineStr"/>
-      <c r="J64" s="10" t="inlineStr"/>
-      <c r="K64" s="10" t="inlineStr"/>
-      <c r="L64" s="10" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr"/>
+      <c r="H69" s="11" t="inlineStr"/>
+      <c r="I69" s="11" t="inlineStr"/>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr"/>
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr">
         <is>
           <t>No public source found</t>
         </is>
       </c>
-      <c r="N64" s="10" t="inlineStr">
+      <c r="N69" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="O64" s="10" t="inlineStr">
+      <c r="O69" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
-      <c r="P64" s="10" t="inlineStr">
+      <c r="P69" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q64" s="10" t="inlineStr">
+      <c r="Q69" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="R64" s="10" t="inlineStr"/>
-      <c r="S64" s="10" t="inlineStr">
+      <c r="R69" s="11" t="inlineStr"/>
+      <c r="S69" s="11" t="inlineStr">
         <is>
           <t>Pawame|Active customers</t>
         </is>
       </c>
-      <c r="T64" s="10" t="inlineStr">
+      <c r="T69" s="11" t="inlineStr">
         <is>
           <t>SR17</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>X-03</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>IFC / AFC material on PAYGo receivables financing</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D70" s="11" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>various</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F70" s="11" t="inlineStr">
         <is>
           <t>Not identified</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr"/>
-      <c r="H65" s="10" t="inlineStr"/>
-      <c r="I65" s="10" t="inlineStr"/>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="G70" s="11" t="inlineStr"/>
+      <c r="H70" s="11" t="inlineStr"/>
+      <c r="I70" s="11" t="inlineStr"/>
+      <c r="J70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr"/>
+      <c r="L70" s="11" t="inlineStr"/>
+      <c r="M70" s="11" t="inlineStr">
         <is>
           <t>Listed for retrieval</t>
         </is>
       </c>
-      <c r="N65" s="10" t="inlineStr">
+      <c r="N70" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="O65" s="10" t="inlineStr">
+      <c r="O70" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
-      <c r="P65" s="10" t="inlineStr">
+      <c r="P70" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q65" s="10" t="inlineStr">
+      <c r="Q70" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R65" s="10" t="inlineStr"/>
-      <c r="S65" s="10" t="inlineStr"/>
-      <c r="T65" s="10" t="inlineStr">
+      <c r="R70" s="11" t="inlineStr"/>
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr">
         <is>
           <t>SR23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T65"/>
+  <autoFilter ref="A1:T70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6501,79 +6951,79 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
+          <t>Ch 1.6, 7.4, 15, 16</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Sector PAYGo collection rate stayed at about 62% from 2021 to 2023</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>E1-14</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Two client extractions agree on the 2021-2023 period; the pages and definition must still be checked against the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
           <t>Ch 1.6, 7.4, 15</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Sector PAYGo collection rate about 62% in 2023</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>E1-14</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Client extraction gives 62% as the 2021-2023 average; the year and definition must be checked against the report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Ch 1.6, 7.4, 15</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>About half of PAYGo customers had been written off or were more than 30 days late</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>E1-16</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>The client extraction concerns about half of companies with write-off ratio plus RAR30 between 30% and 50%. Withdraw the book's wording.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Ch 15</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>M-KOPA FY2024 revenue USD 416m or USD 253.5m; net profit USD 9.2m</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>E4-01 to E4-08</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>The primary filing held is a UK subsidiary (GBP 1.7m revenue from carbon credits). Remove the '6.1 times' diagnostic; keep the conflict as an illustration of entity checking.</t>
         </is>
@@ -6634,27 +7084,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Ch 7.1</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>PERFORM standardises collection rate, receivables at risk and write offs, later adding repayment and ownership rates</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>E2-01, E2-06</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>VERIFIED (HISTORICAL)</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Restructure Chapter 7 on the 2026 standard (change B4).</t>
         </is>
@@ -6715,120 +7165,120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>E1-16</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Share of companies with write-off ratio plus RAR30 between 30% and 50%</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>about 50% (18% in 2021)</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>% of companies</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>E1-30</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>World Bank lending to governments for off-grid solar, FY2024</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>about 660 or 626</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>ESMAP / World Bank, with GOGLA and Dalberg (as reported): Off-Grid Solar Market Trends Report 2024</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>CONFLICTS WITH THE BOOK'S WORDING: the client extraction concerns half of companies within a ratio band, not half of customers. Book wording to be withdrawn. RAR30 and write-off ratio are 2021 PERFORM portfolio quality metrics (E2a-03, E2a-04).</t>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>The second client extraction reports both figures in different sections of the report. Not used until checked in the document.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>E4-04</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>M-KOPA group revenue FY2024</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="8" t="n">
         <v>416</v>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>TechCabal: News article citing 'UK filings'</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Conflicts with E4-05 (USD 253.5m). Not supported by E4-01 (different entity). Resolvable only with the consolidated accounts of the reporting group entity.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>E4-05</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>M-KOPA group revenue FY2024</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="8" t="n">
         <v>253.5</v>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Kenyan Wall Street: News article</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>E4-08</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>M-KOPA group net result, prior year</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>-24.7 (or -20.6)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>TechCabal; Kenyan Wall Street: News articles</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6867,17 +7317,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>SR01</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>E4-04</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
@@ -6918,17 +7368,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>SR04</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>E4-08</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
@@ -7003,17 +7453,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>SR09</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>E5-05</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
@@ -7071,17 +7521,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>SR13</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>E6-04</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
@@ -7122,34 +7572,34 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>SR16</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>X-01</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>SR17</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>X-02</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
@@ -7207,51 +7657,51 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>SR21</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>E2-06</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>VERIFIED (HISTORICAL)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>SR22</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>E2d-01</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>SR23</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>X-03</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>

--- a/output/04_SOURCE_REGISTER_v1.0.xlsx
+++ b/output/04_SOURCE_REGISTER_v1.0.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy_Map" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$T$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Register'!$A$1:$T$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T70"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4642,86 +4642,94 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>E3-01</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>Multi-Tier Framework capacity thresholds (T4 at least 800 W / 3.4 kWh a day; T5 at least 2 kW / 8.2 kWh a day)</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Multi-Tier Framework household electricity supply, capacity: Tier 1 min 3 W or 12 Wh a day; Tier 2 min 50 W or 200 Wh; Tier 3 min 200 W or 1.0 kWh; Tier 4 min 800 W or 3.4 kWh; Tier 5 min 2 kW or 8.2 kWh</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>T1-T5</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>Beyond Connections: Energy Access Redefined</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Beyond Connections: Energy Access Redefined (Technical Report 008/15, conceptualization report)</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>ESMAP / World Bank</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Not held</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>Thresholds recorded from earlier research; framework report not read</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>July 2015</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>BEYOND CONNECTIONS  Energy Access Redefined.pdf (244 pages; author's Google Drive, SHA-256 9d23881a...c1d26b)</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>20 (report page 6)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>Table ES.1, Multi-tier Matrix for Measuring Access to Household Electricity Supply</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>Project file (retrieved from the author's Drive, 4 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>Read in the document</t>
+        </is>
+      </c>
+      <c r="N45" s="9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O45" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P45" s="7" t="inlineStr">
+      <c r="O45" s="9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P45" s="9" t="inlineStr">
         <is>
           <t>Ch 2.6</t>
         </is>
       </c>
-      <c r="Q45" s="7" t="inlineStr">
-        <is>
-          <t>Products tier labels</t>
-        </is>
-      </c>
-      <c r="R45" s="7" t="inlineStr"/>
-      <c r="S45" s="7" t="inlineStr"/>
-      <c r="T45" s="7" t="inlineStr">
+      <c r="Q45" s="9" t="inlineStr">
+        <is>
+          <t>Products tier labels (capacity attribute only)</t>
+        </is>
+      </c>
+      <c r="R45" s="9" t="inlineStr"/>
+      <c r="S45" s="9" t="inlineStr"/>
+      <c r="T45" s="9" t="inlineStr">
         <is>
           <t>SR20</t>
         </is>
@@ -4730,70 +4738,72 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>E4-01</t>
+          <t>E3-02</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>M-KOPA UK LIMITED revenue (sales of carbon credits)</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>1712776</v>
+          <t>Household electricity attributes are capacity, duration (daily and evening supply), reliability, quality, affordability, legality, and health and safety; the lowest tier among all attributes determines the household's overall tier</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>FY2024 (FY2023: 718,100)</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
+          <t>Beyond Connections: Energy Access Redefined (Technical Report 008/15, conceptualization report)</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>Companies House (company 10229661)</t>
+          <t>ESMAP / World Bank</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
+          <t>July 2015</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
+          <t>BEYOND CONNECTIONS  Energy Access Redefined.pdf (244 pages; author's Google Drive, SHA-256 9d23881a...c1d26b)</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>10 (filing page 8); 18 (filing page 16, note 2.1)</t>
+          <t>19 (report page 5)</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>Statement of profit or loss; note 2.1 Sale of carbon credits</t>
+          <t>Executive Summary</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
+          <t>Project file (retrieved from the author's Drive, 4 Oct 2026)</t>
         </is>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
+          <t>Read in the document</t>
         </is>
       </c>
       <c r="N46" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O46" s="9" t="inlineStr">
@@ -4803,89 +4813,87 @@
       </c>
       <c r="P46" s="9" t="inlineStr">
         <is>
-          <t>Planned: Ch 15 (as an illustration of entity checking)</t>
+          <t>Ch 2.6</t>
         </is>
       </c>
       <c r="Q46" s="9" t="inlineStr">
         <is>
-          <t>Not used: different entity and activity; not a PAYGo benchmark</t>
-        </is>
-      </c>
-      <c r="R46" s="9" t="inlineStr">
-        <is>
-          <t>UK research and development subsidiary; no employees; functional currency sterling; IFRS as adopted in the UK; not consolidated.</t>
-        </is>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R46" s="9" t="inlineStr"/>
       <c r="S46" s="9" t="inlineStr"/>
       <c r="T46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>E4-02</t>
+          <t>E3-03</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>M-KOPA UK LIMITED profit for the year</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>1040472</v>
+          <t>Duration thresholds: Tier 1 min 4 hours a day and 1 evening hour; Tier 2 min 4 hours and 2 evening hours; affordability attribute met when a standard package of 365 kWh a year costs less than 5% of household income</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>thresholds</t>
+        </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>FY2024 (FY2023: 497,346)</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
+          <t>Beyond Connections: Energy Access Redefined (Technical Report 008/15, conceptualization report)</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>Companies House (company 10229661)</t>
+          <t>ESMAP / World Bank</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
+          <t>July 2015</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
+          <t>BEYOND CONNECTIONS  Energy Access Redefined.pdf (244 pages; author's Google Drive, SHA-256 9d23881a...c1d26b)</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>10 (filing page 8)</t>
+          <t>20 (report page 6)</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>Statement of profit or loss</t>
+          <t>Table ES.1</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>Project file (uploaded 3 Oct 2026)</t>
+          <t>Project file (retrieved from the author's Drive, 4 Oct 2026)</t>
         </is>
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
+          <t>Read in the document</t>
         </is>
       </c>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O47" s="9" t="inlineStr">
@@ -4895,42 +4903,44 @@
       </c>
       <c r="P47" s="9" t="inlineStr">
         <is>
+          <t>Ch 2.6</t>
+        </is>
+      </c>
+      <c r="Q47" s="9" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q47" s="9" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="R47" s="9" t="inlineStr"/>
+      <c r="R47" s="9" t="inlineStr">
+        <is>
+          <t>The MTF affordability test prices a standard consumption package, not a PAYGo instalment; it is a different measure from the payment burden in Ch 2.3.</t>
+        </is>
+      </c>
       <c r="S47" s="9" t="inlineStr"/>
       <c r="T47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>E4-03</t>
+          <t>E4-01</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>M-KOPA UK LIMITED parent and ultimate parent: M-Kopa LLC (Delaware); M-Kopa Holdings Limited (London)</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
+          <t>M-KOPA UK LIMITED revenue (sales of carbon credits)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>1712776</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (FY2023: 718,100)</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -4955,12 +4965,12 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>3 (filing page 1)</t>
+          <t>10 (filing page 8); 18 (filing page 16, note 2.1)</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>Company information</t>
+          <t>Statement of profit or loss; note 2.1 Sale of carbon credits</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
@@ -4985,489 +4995,489 @@
       </c>
       <c r="P48" s="9" t="inlineStr">
         <is>
-          <t>Planned: Ch 15</t>
+          <t>Planned: Ch 15 (as an illustration of entity checking)</t>
         </is>
       </c>
       <c r="Q48" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Not used: different entity and activity; not a PAYGo benchmark</t>
         </is>
       </c>
       <c r="R48" s="9" t="inlineStr">
         <is>
-          <t>The project's benchmark files attribute the group figures to M-KOPA Holdings Ltd, Companies House 10891868. That number has not been checked against the register.</t>
+          <t>UK research and development subsidiary; no employees; functional currency sterling; IFRS as adopted in the UK; not consolidated.</t>
         </is>
       </c>
       <c r="S48" s="9" t="inlineStr"/>
       <c r="T48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>E4-02</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED profit for the year</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>1040472</v>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>FY2024 (FY2023: 497,346)</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Companies House (company 10229661)</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>10 (filing page 8)</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>Statement of profit or loss</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
+        </is>
+      </c>
+      <c r="N49" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P49" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q49" s="9" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+      <c r="R49" s="9" t="inlineStr"/>
+      <c r="S49" s="9" t="inlineStr"/>
+      <c r="T49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>E4-03</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED parent and ultimate parent: M-Kopa LLC (Delaware); M-Kopa Holdings Limited (London)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>M-KOPA UK LIMITED, Annual Report and Accounts, year ended 31 December 2024</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Companies House (company 10229661)</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Approved 20 Jun 2025; filed 25 Sep 2025</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>245b3bf6-companies_house_document.pdf (34 pages, scanned)</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>3 (filing page 1)</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>Company information</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>Project file (uploaded 3 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>Audited statutory accounts (auditor KLSA LLP), read page by page</t>
+        </is>
+      </c>
+      <c r="N50" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P50" s="9" t="inlineStr">
+        <is>
+          <t>Planned: Ch 15</t>
+        </is>
+      </c>
+      <c r="Q50" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R50" s="9" t="inlineStr">
+        <is>
+          <t>The project's benchmark files attribute the group figures to M-KOPA Holdings Ltd, Companies House 10891868. That number has not been checked against the register.</t>
+        </is>
+      </c>
+      <c r="S50" s="9" t="inlineStr"/>
+      <c r="T50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>E4-04</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>M-KOPA group revenue FY2024</t>
         </is>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C51" s="8" t="n">
         <v>416</v>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>News article citing 'UK filings'</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>TechCabal</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>7 Oct 2025</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>Web article</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr"/>
-      <c r="L49" s="8" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr"/>
+      <c r="L51" s="8" t="inlineStr">
         <is>
           <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
         </is>
       </c>
-      <c r="M49" s="8" t="inlineStr">
+      <c r="M51" s="8" t="inlineStr">
         <is>
           <t>Secondary report; entity and revenue line not identified</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr">
+      <c r="N51" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O51" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
       </c>
-      <c r="P49" s="8" t="inlineStr">
+      <c r="P51" s="8" t="inlineStr">
         <is>
           <t>Ch 15 (presented as conflicting)</t>
         </is>
       </c>
-      <c r="Q49" s="8" t="inlineStr">
+      <c r="Q51" s="8" t="inlineStr">
         <is>
           <t>Market_Benchmark and Calibration: suspended</t>
         </is>
       </c>
-      <c r="R49" s="8" t="inlineStr">
+      <c r="R51" s="8" t="inlineStr">
         <is>
           <t>Conflicts with E4-05 (USD 253.5m). Not supported by E4-01 (different entity). Resolvable only with the consolidated accounts of the reporting group entity.</t>
         </is>
       </c>
-      <c r="S49" s="8" t="inlineStr">
+      <c r="S51" s="8" t="inlineStr">
         <is>
           <t>M-KOPA|Revenue</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>SR01</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>E4-05</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>M-KOPA group revenue FY2024</t>
         </is>
       </c>
-      <c r="C50" s="8" t="n">
+      <c r="C52" s="8" t="n">
         <v>253.5</v>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>News article</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Kenyan Wall Street</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Web article</t>
         </is>
       </c>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K50" s="8" t="inlineStr"/>
-      <c r="L50" s="8" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr"/>
+      <c r="L52" s="8" t="inlineStr">
         <is>
           <t>https://kenyanwallstreet.com/m-kopa-posts-first-ever-profit-bets-on-e-mobility-for-next-growth-phase/</t>
         </is>
       </c>
-      <c r="M50" s="8" t="inlineStr">
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>Secondary report; may be a different revenue line</t>
         </is>
       </c>
-      <c r="N50" s="8" t="inlineStr">
+      <c r="N52" s="8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O52" s="8" t="inlineStr">
         <is>
           <t>CONFLICTING SOURCES</t>
         </is>
       </c>
-      <c r="P50" s="8" t="inlineStr">
+      <c r="P52" s="8" t="inlineStr">
         <is>
           <t>Ch 15 (presented as conflicting)</t>
         </is>
       </c>
-      <c r="Q50" s="8" t="inlineStr">
+      <c r="Q52" s="8" t="inlineStr">
         <is>
           <t>Not used</t>
         </is>
       </c>
-      <c r="R50" s="8" t="inlineStr"/>
-      <c r="S50" s="8" t="inlineStr"/>
-      <c r="T50" s="8" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="R52" s="8" t="inlineStr"/>
+      <c r="S52" s="8" t="inlineStr"/>
+      <c r="T52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>E4-06</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>M-KOPA group revenue growth</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C53" s="7" t="n">
         <v>0.66</v>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>FY2024 vs FY2023</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>News articles</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>TechCabal; Kenyan Wall Street</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>Oct 2025</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Web articles</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>Secondary report</t>
         </is>
       </c>
-      <c r="N51" s="7" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O51" s="7" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>PENDING PRIMARY DOCUMENT</t>
         </is>
       </c>
-      <c r="P51" s="7" t="inlineStr">
+      <c r="P53" s="7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q51" s="7" t="inlineStr">
+      <c r="Q53" s="7" t="inlineStr">
         <is>
           <t>Calibration growth reference: suspended</t>
         </is>
       </c>
-      <c r="R51" s="7" t="inlineStr"/>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="R53" s="7" t="inlineStr"/>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>M-KOPA|Revenue growth</t>
         </is>
       </c>
-      <c r="T51" s="7" t="inlineStr">
+      <c r="T53" s="7" t="inlineStr">
         <is>
           <t>SR02</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>E4-07</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>M-KOPA group net profit</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>USD m</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>News article</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>TechCabal</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>7 Oct 2025</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Web article</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
-        </is>
-      </c>
-      <c r="M52" s="7" t="inlineStr">
-        <is>
-          <t>Secondary report</t>
-        </is>
-      </c>
-      <c r="N52" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O52" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P52" s="7" t="inlineStr">
-        <is>
-          <t>Ch 15</t>
-        </is>
-      </c>
-      <c r="Q52" s="7" t="inlineStr">
-        <is>
-          <t>Calibration net margin reference: suspended</t>
-        </is>
-      </c>
-      <c r="R52" s="7" t="inlineStr"/>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>M-KOPA|Net profit</t>
-        </is>
-      </c>
-      <c r="T52" s="7" t="inlineStr">
-        <is>
-          <t>SR03</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>E4-08</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>M-KOPA group net result, prior year</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>-24.7 (or -20.6)</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>USD m</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>News articles</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>TechCabal; Kenyan Wall Street</t>
-        </is>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>Web articles</t>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K53" s="8" t="inlineStr"/>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
-        </is>
-      </c>
-      <c r="M53" s="8" t="inlineStr">
-        <is>
-          <t>Secondary reports that conflict</t>
-        </is>
-      </c>
-      <c r="N53" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O53" s="8" t="inlineStr">
-        <is>
-          <t>CONFLICTING SOURCES</t>
-        </is>
-      </c>
-      <c r="P53" s="8" t="inlineStr">
-        <is>
-          <t>Ch 15</t>
-        </is>
-      </c>
-      <c r="Q53" s="8" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="R53" s="8" t="inlineStr"/>
-      <c r="S53" s="8" t="inlineStr"/>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>SR04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>E5-01</t>
+          <t>E4-07</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Sun King cumulative solar loans</t>
+          <t>M-KOPA group net profit</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>1300</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
@@ -5476,27 +5486,27 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Cumulative to Jul 2025</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Citi press release on the Sun King securitisation</t>
+          <t>News article</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>TechCabal</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>7 Oct 2025</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Press release (not read in this project)</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
@@ -5507,17 +5517,17 @@
       <c r="K54" s="7" t="inlineStr"/>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
+          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
         <is>
-          <t>Company disclosure recorded from earlier research</t>
+          <t>Secondary report</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O54" s="7" t="inlineStr">
@@ -5527,131 +5537,129 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>Ch 12, 15</t>
+          <t>Ch 15</t>
         </is>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
-          <t>Market_Benchmark (shown, flagged)</t>
+          <t>Calibration net margin reference: suspended</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr"/>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>Sun King|Cumulative solar loans</t>
+          <t>M-KOPA|Net profit</t>
         </is>
       </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
-          <t>SR05</t>
+          <t>SR03</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>E5-02</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Sun King cumulative loan customers (cumulative, not active)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>million</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Cumulative to Jul 2025</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>Citi press release</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>Citigroup</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>E4-08</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>M-KOPA group net result, prior year</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>-24.7 (or -20.6)</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>News articles</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>TechCabal; Kenyan Wall Street</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Press release (not read)</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>Web articles</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>PAGE TO VERIFY</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>Company disclosure recorded from earlier research</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="O55" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P55" s="7" t="inlineStr">
-        <is>
-          <t>Ch 12, 15</t>
-        </is>
-      </c>
-      <c r="Q55" s="7" t="inlineStr">
-        <is>
-          <t>Market_Benchmark (shown, flagged)</t>
-        </is>
-      </c>
-      <c r="R55" s="7" t="inlineStr"/>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>Sun King|Cumulative loan customers</t>
-        </is>
-      </c>
-      <c r="T55" s="7" t="inlineStr">
-        <is>
-          <t>SR06</t>
+      <c r="K55" s="8" t="inlineStr"/>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>https://techcabal.com/2025/10/07/m-kopa-turns-first-ever-profit-revenue-surges-66-416/</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="inlineStr">
+        <is>
+          <t>Secondary reports that conflict</t>
+        </is>
+      </c>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>CONFLICTING SOURCES</t>
+        </is>
+      </c>
+      <c r="P55" s="8" t="inlineStr">
+        <is>
+          <t>Ch 15</t>
+        </is>
+      </c>
+      <c r="Q55" s="8" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+      <c r="R55" s="8" t="inlineStr"/>
+      <c r="S55" s="8" t="inlineStr"/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>SR04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>E5-03</t>
+          <t>E5-01</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Sun King local-currency securitisation in Kenya</t>
+          <t>Sun King cumulative solar loans</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>130</v>
+        <v>1300</v>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
@@ -5660,27 +5668,27 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>May 2023</t>
+          <t>Cumulative to Jul 2025</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Sun King news release</t>
+          <t>Citi press release on the Sun King securitisation</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Sun King</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>News release (not read)</t>
+          <t>Press release (not read in this project)</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
@@ -5691,7 +5699,7 @@
       <c r="K56" s="7" t="inlineStr"/>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>https://sunking.com/news-blog/sun-king-and-citi-close-first-130-million-securitisation-to-broaden-access-to-finance-for-off-grid-solar-in-kenya/</t>
+          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -5711,64 +5719,68 @@
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>Ch 3.11, 11, 12</t>
+          <t>Ch 12, 15</t>
         </is>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Market_Benchmark (shown, flagged)</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr"/>
-      <c r="S56" s="7" t="inlineStr"/>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>Sun King|Cumulative solar loans</t>
+        </is>
+      </c>
       <c r="T56" s="7" t="inlineStr">
         <is>
-          <t>SR07</t>
+          <t>SR05</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>E5-04</t>
+          <t>E5-02</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Sun King local-currency securitisation in Kenya (KES 20.1bn)</t>
+          <t>Sun King cumulative loan customers (cumulative, not active)</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>million</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Jul 2025</t>
+          <t>Cumulative to Jul 2025</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Citi release; trade press</t>
+          <t>Citi press release</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Citigroup; pv magazine</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>29 Jul 2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Release and article (not read)</t>
+          <t>Press release (not read)</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
@@ -5779,12 +5791,12 @@
       <c r="K57" s="7" t="inlineStr"/>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2025/07/29/sun-king-closes-156m-off-grid-solar-deal-in-kenya/</t>
+          <t>https://www.citigroup.com/global/news/press-release/2025/citi-sun-king-securitization-deliver-solar-million-kenyans</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
         <is>
-          <t>Company disclosure and secondary report recorded from earlier research</t>
+          <t>Company disclosure recorded from earlier research</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
@@ -5799,7 +5811,7 @@
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>Ch 3.11, 11, 12</t>
+          <t>Ch 12, 15</t>
         </is>
       </c>
       <c r="Q57" s="7" t="inlineStr">
@@ -5810,96 +5822,116 @@
       <c r="R57" s="7" t="inlineStr"/>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>Sun King|Securitisation 2025</t>
+          <t>Sun King|Cumulative loan customers</t>
         </is>
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>SR08</t>
+          <t>SR06</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>E5-05</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>Sun King MSME bond</t>
-        </is>
-      </c>
-      <c r="C58" s="11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>E5-03</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Sun King local-currency securitisation in Kenya</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="G58" s="11" t="inlineStr"/>
-      <c r="H58" s="11" t="inlineStr"/>
-      <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="11" t="inlineStr"/>
-      <c r="K58" s="11" t="inlineStr"/>
-      <c r="L58" s="11" t="inlineStr"/>
-      <c r="M58" s="11" t="inlineStr">
-        <is>
-          <t>No public source found</t>
-        </is>
-      </c>
-      <c r="N58" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="O58" s="11" t="inlineStr">
-        <is>
-          <t>NOT USED</t>
-        </is>
-      </c>
-      <c r="P58" s="11" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>May 2023</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Sun King news release</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Sun King</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>News release (not read)</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>https://sunking.com/news-blog/sun-king-and-citi-close-first-130-million-securitisation-to-broaden-access-to-finance-for-off-grid-solar-in-kenya/</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>Company disclosure recorded from earlier research</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O58" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>Ch 3.11, 11, 12</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q58" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="R58" s="11" t="inlineStr"/>
-      <c r="S58" s="11" t="inlineStr"/>
-      <c r="T58" s="11" t="inlineStr">
-        <is>
-          <t>SR09</t>
+      <c r="R58" s="7" t="inlineStr"/>
+      <c r="S58" s="7" t="inlineStr"/>
+      <c r="T58" s="7" t="inlineStr">
+        <is>
+          <t>SR07</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>E6-01</t>
+          <t>E5-04</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>d.light securitisation purchasing capacity since 2020 (five facilities; purchasing capacity, not debt raised)</t>
+          <t>Sun King local-currency securitisation in Kenya (KES 20.1bn)</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>718</v>
+        <v>156</v>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
@@ -5908,27 +5940,27 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>2020 to Jul 2024</t>
+          <t>Jul 2025</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>News article</t>
+          <t>Citi release; trade press</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Techpoint Africa</t>
+          <t>Citigroup; pv magazine</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>17 Jul 2024</t>
+          <t>29 Jul 2025</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
+          <t>Release and article (not read)</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
@@ -5939,17 +5971,17 @@
       <c r="K59" s="7" t="inlineStr"/>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
+          <t>https://www.pv-magazine.com/2025/07/29/sun-king-closes-156m-off-grid-solar-deal-in-kenya/</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
         <is>
-          <t>Secondary report</t>
+          <t>Company disclosure and secondary report recorded from earlier research</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O59" s="7" t="inlineStr">
@@ -5959,7 +5991,7 @@
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>Ch 3.11, 11, 12, 15</t>
+          <t>Ch 3.11, 11, 12</t>
         </is>
       </c>
       <c r="Q59" s="7" t="inlineStr">
@@ -5970,149 +6002,125 @@
       <c r="R59" s="7" t="inlineStr"/>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>d.light|Securitisation purchasing capacity since 2020</t>
+          <t>Sun King|Securitisation 2025</t>
         </is>
       </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
-          <t>SR10</t>
+          <t>SR08</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>E6-02</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>d.light multi-currency securitisation facility</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>176</v>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>E5-05</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Sun King MSME bond</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Jul 2024</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>News articles</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Techpoint Africa; WeeTracker</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>17 Jul 2024</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Web articles</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
-        </is>
-      </c>
-      <c r="M60" s="7" t="inlineStr">
-        <is>
-          <t>Secondary report</t>
-        </is>
-      </c>
-      <c r="N60" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O60" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P60" s="7" t="inlineStr">
-        <is>
-          <t>Ch 12</t>
-        </is>
-      </c>
-      <c r="Q60" s="7" t="inlineStr">
-        <is>
-          <t>Market_Benchmark (shown, flagged)</t>
-        </is>
-      </c>
-      <c r="R60" s="7" t="inlineStr"/>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>d.light|Securitisation facility 2024</t>
-        </is>
-      </c>
-      <c r="T60" s="7" t="inlineStr">
-        <is>
-          <t>SR11</t>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr"/>
+      <c r="I60" s="11" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr"/>
+      <c r="L60" s="11" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>No public source found</t>
+        </is>
+      </c>
+      <c r="N60" s="11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O60" s="11" t="inlineStr">
+        <is>
+          <t>NOT USED</t>
+        </is>
+      </c>
+      <c r="P60" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q60" s="11" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="R60" s="11" t="inlineStr"/>
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr">
+        <is>
+          <t>SR09</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>E6-03</t>
+          <t>E6-01</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>d.light revenue growth</t>
+          <t>d.light securitisation purchasing capacity since 2020 (five facilities; purchasing capacity, not debt raised)</t>
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0.41</v>
+        <v>718</v>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>USD m</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>H1 2023 vs H1 2022</t>
+          <t>2020 to Jul 2024</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>d.light press release</t>
+          <t>News article</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>d.light via PR Newswire</t>
+          <t>Techpoint Africa</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Sep 2023</t>
+          <t>17 Jul 2024</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Press release (not read)</t>
+          <t>Web article</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
@@ -6123,17 +6131,17 @@
       <c r="K61" s="7" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.co.uk/news-releases/dlight-revenues-surge-by-41-percent-in-first-six-months-of-2023-driven-by-143-percent-growth-in-nigeria-301919233.html</t>
+          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>Company disclosure recorded from earlier research</t>
+          <t>Secondary report</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -6143,7 +6151,7 @@
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ch 3.11, 11, 12, 15</t>
         </is>
       </c>
       <c r="Q61" s="7" t="inlineStr">
@@ -6154,164 +6162,170 @@
       <c r="R61" s="7" t="inlineStr"/>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>d.light|Revenue growth</t>
+          <t>d.light|Securitisation purchasing capacity since 2020</t>
         </is>
       </c>
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>SR12</t>
+          <t>SR10</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>E6-04</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>d.light revenue (third-party estimate)</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>301.2</v>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>E6-02</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>d.light multi-currency securitisation facility</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>USD m</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>Company database</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>bitscale.ai</t>
-        </is>
-      </c>
-      <c r="H62" s="11" t="inlineStr">
-        <is>
-          <t>n/d</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>Web page</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr"/>
-      <c r="K62" s="11" t="inlineStr"/>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>https://www.bitscale.ai/directory/dlight</t>
-        </is>
-      </c>
-      <c r="M62" s="11" t="inlineStr">
-        <is>
-          <t>Third-party estimate, method not stated</t>
-        </is>
-      </c>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="O62" s="11" t="inlineStr">
-        <is>
-          <t>NOT USED</t>
-        </is>
-      </c>
-      <c r="P62" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q62" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="R62" s="11" t="inlineStr"/>
-      <c r="S62" s="11" t="inlineStr"/>
-      <c r="T62" s="11" t="inlineStr">
-        <is>
-          <t>SR13</t>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2024</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>News articles</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Techpoint Africa; WeeTracker</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>17 Jul 2024</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>Web articles</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>https://techpoint.africa/2024/07/17/d-light-raises-176m/</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>Secondary report</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O62" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>Ch 12</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>Market_Benchmark (shown, flagged)</t>
+        </is>
+      </c>
+      <c r="R62" s="7" t="inlineStr"/>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>d.light|Securitisation facility 2024</t>
+        </is>
+      </c>
+      <c r="T62" s="7" t="inlineStr">
+        <is>
+          <t>SR11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>E7-01</t>
+          <t>E6-03</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>BBOXX LTD (07177839): appointment of administrators</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>19 May 2025</t>
-        </is>
+          <t>d.light revenue growth</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>0.41</v>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>H1 2023 vs H1 2022</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Notice of appointment of administrators</t>
+          <t>d.light press release</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>The Gazette</t>
+          <t>d.light via PR Newswire</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>2025 (to verify)</t>
+          <t>Sep 2023</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Gazette notice 4891954 (not held)</t>
+          <t>Press release (not read)</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>Notice</t>
+          <t>PAGE TO VERIFY</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr"/>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>https://www.thegazette.co.uk/notice/4891954 (not opened from this environment)</t>
+          <t>https://www.prnewswire.co.uk/news-releases/dlight-revenues-surge-by-41-percent-in-first-six-months-of-2023-driven-by-143-percent-growth-in-nigeria-301919233.html</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>Date recorded from earlier research (Gazette and administrator's announcement); notice not read in this project</t>
+          <t>Company disclosure recorded from earlier research</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
@@ -6321,144 +6335,144 @@
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>Ch 1.6, 14</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
-          <t>Company_Cases text</t>
-        </is>
-      </c>
-      <c r="R63" s="7" t="inlineStr">
-        <is>
-          <t>The date must be the date of appointment stated in the formal notice, not a petition, hearing, publication or creditors' meeting date.</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr"/>
+          <t>Market_Benchmark (shown, flagged)</t>
+        </is>
+      </c>
+      <c r="R63" s="7" t="inlineStr"/>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>d.light|Revenue growth</t>
+        </is>
+      </c>
       <c r="T63" s="7" t="inlineStr">
         <is>
-          <t>SR15</t>
+          <t>SR12</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>E7-02</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>BBOXX LTD (07177839): latest filed accounts made up to 31 Dec 2022; FY2023 accounts overdue; status in administration</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Companies House register</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Companies House</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>2025 (to verify)</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>Register entry (not opened)</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr"/>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07177839 (not opened from this environment)</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="inlineStr">
-        <is>
-          <t>Recorded from earlier research</t>
-        </is>
-      </c>
-      <c r="N64" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O64" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
-        </is>
-      </c>
-      <c r="P64" s="7" t="inlineStr">
-        <is>
-          <t>Ch 1.6</t>
-        </is>
-      </c>
-      <c r="Q64" s="7" t="inlineStr">
-        <is>
-          <t>Company_Cases text</t>
-        </is>
-      </c>
-      <c r="R64" s="7" t="inlineStr"/>
-      <c r="S64" s="7" t="inlineStr"/>
-      <c r="T64" s="7" t="inlineStr">
-        <is>
-          <t>SR14</t>
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>E6-04</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>d.light revenue (third-party estimate)</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>301.2</v>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>Company database</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>bitscale.ai</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr"/>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>https://www.bitscale.ai/directory/dlight</t>
+        </is>
+      </c>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>Third-party estimate, method not stated</t>
+        </is>
+      </c>
+      <c r="N64" s="11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O64" s="11" t="inlineStr">
+        <is>
+          <t>NOT USED</t>
+        </is>
+      </c>
+      <c r="P64" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q64" s="11" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="R64" s="11" t="inlineStr"/>
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr">
+        <is>
+          <t>SR13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>E8-01</t>
+          <t>E7-01</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Off-grid solar investment in 2024, down about 30%</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="n">
-        <v>299</v>
+          <t>BBOXX LTD (07177839): appointment of administrators</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>19 May 2025</t>
+        </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>GOGLA investment data (as reported)</t>
+          <t>Notice of appointment of administrators</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>GOGLA</t>
+          <t>The Gazette</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -6468,24 +6482,28 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>Not held</t>
+          <t>Gazette notice 4891954 (not held)</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>PAGE TO VERIFY</t>
+          <t>Notice</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr"/>
-      <c r="L65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.thegazette.co.uk/notice/4891954 (not opened from this environment)</t>
+        </is>
+      </c>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>Secondary report</t>
+          <t>Date recorded from earlier research (Gazette and administrator's announcement); notice not read in this project</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O65" s="7" t="inlineStr">
@@ -6495,85 +6513,87 @@
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>Ch 11.1, 14</t>
+          <t>Ch 1.6, 14</t>
         </is>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Company_Cases text</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>Consistency only, not verification: E1-17 gives USD 425m for 2023, and 425 x 0.7 is about 298.</t>
+          <t>The date must be the date of appointment stated in the formal notice, not a petition, hearing, publication or creditors' meeting date.</t>
         </is>
       </c>
       <c r="S65" s="7" t="inlineStr"/>
-      <c r="T65" s="7" t="inlineStr"/>
+      <c r="T65" s="7" t="inlineStr">
+        <is>
+          <t>SR15</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>E9-01</t>
+          <t>E7-02</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>ZOLA Electric financing round (USD 45m equity, USD 45m debt)</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>90</v>
+          <t>BBOXX LTD (07177839): latest filed accounts made up to 31 Dec 2022; FY2023 accounts overdue; status in administration</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>USD m</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>News article</t>
+          <t>Companies House register</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>TechCrunch</t>
+          <t>Companies House</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>23 Sep 2021</t>
+          <t>2025 (to verify)</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>Web article</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr">
-        <is>
-          <t>PAGE TO VERIFY</t>
-        </is>
-      </c>
+          <t>Register entry (not opened)</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr"/>
       <c r="K66" s="7" t="inlineStr"/>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2021/09/23/zola-electric-closes-90m-funding-round-to-scale-technology-and-enter-new-markets</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07177839 (not opened from this environment)</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>Secondary report</t>
+          <t>Recorded from earlier research</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O66" s="7" t="inlineStr">
@@ -6583,65 +6603,59 @@
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ch 1.6</t>
         </is>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
-          <t>Market_Benchmark (shown, flagged)</t>
+          <t>Company_Cases text</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr"/>
-      <c r="S66" s="7" t="inlineStr">
-        <is>
-          <t>ZOLA Electric|Financing round</t>
-        </is>
-      </c>
+      <c r="S66" s="7" t="inlineStr"/>
       <c r="T66" s="7" t="inlineStr">
         <is>
-          <t>SR18</t>
+          <t>SR14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>E10-01</t>
+          <t>E8-01</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>SEforALL Universal Energy Facility pays results-based finance per verified connection</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>qualitative</t>
-        </is>
+          <t>Off-grid solar investment in 2024, down about 30%</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>299</v>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>USD m</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>SEforALL (as reported)</t>
+          <t>GOGLA investment data (as reported)</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>SEforALL</t>
+          <t>GOGLA</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>to verify</t>
+          <t>2025 (to verify)</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -6658,7 +6672,7 @@
       <c r="L67" s="7" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>Secondary description</t>
+          <t>Secondary report</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
@@ -6673,7 +6687,7 @@
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>Ch 13.2</t>
+          <t>Ch 11.1, 14</t>
         </is>
       </c>
       <c r="Q67" s="7" t="inlineStr">
@@ -6681,183 +6695,215 @@
           <t>None</t>
         </is>
       </c>
-      <c r="R67" s="7" t="inlineStr"/>
+      <c r="R67" s="7" t="inlineStr">
+        <is>
+          <t>Consistency only, not verification: E1-17 gives USD 425m for 2023, and 425 x 0.7 is about 298.</t>
+        </is>
+      </c>
       <c r="S67" s="7" t="inlineStr"/>
       <c r="T67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>X-01</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>Pawame SHS financed</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="n">
-        <v>18700</v>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>E9-01</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>ZOLA Electric financing round (USD 45m equity, USD 45m debt)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2021</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>News article</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>23 Sep 2021</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>Web article</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2021/09/23/zola-electric-closes-90m-funding-round-to-scale-technology-and-enter-new-markets</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>Secondary report</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>Market_Benchmark (shown, flagged)</t>
+        </is>
+      </c>
+      <c r="R68" s="7" t="inlineStr"/>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>ZOLA Electric|Financing round</t>
+        </is>
+      </c>
+      <c r="T68" s="7" t="inlineStr">
+        <is>
+          <t>SR18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>E10-01</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>SEforALL Universal Energy Facility pays results-based finance per verified connection</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>qualitative</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="G68" s="11" t="inlineStr"/>
-      <c r="H68" s="11" t="inlineStr"/>
-      <c r="I68" s="11" t="inlineStr"/>
-      <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="11" t="inlineStr"/>
-      <c r="L68" s="11" t="inlineStr"/>
-      <c r="M68" s="11" t="inlineStr">
-        <is>
-          <t>No public source found</t>
-        </is>
-      </c>
-      <c r="N68" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>NOT USED</t>
-        </is>
-      </c>
-      <c r="P68" s="11" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>SEforALL (as reported)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>SEforALL</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>to verify</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Not held</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>PAGE TO VERIFY</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>Secondary description</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O69" s="7" t="inlineStr">
+        <is>
+          <t>PENDING PRIMARY DOCUMENT</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>Ch 13.2</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q68" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="R68" s="11" t="inlineStr"/>
-      <c r="S68" s="11" t="inlineStr">
-        <is>
-          <t>Pawame|SHS financed</t>
-        </is>
-      </c>
-      <c r="T68" s="11" t="inlineStr">
-        <is>
-          <t>SR16</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>X-02</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>Pawame active customers</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="n">
-        <v>16000</v>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>customers</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="G69" s="11" t="inlineStr"/>
-      <c r="H69" s="11" t="inlineStr"/>
-      <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="11" t="inlineStr"/>
-      <c r="K69" s="11" t="inlineStr"/>
-      <c r="L69" s="11" t="inlineStr"/>
-      <c r="M69" s="11" t="inlineStr">
-        <is>
-          <t>No public source found</t>
-        </is>
-      </c>
-      <c r="N69" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="O69" s="11" t="inlineStr">
-        <is>
-          <t>NOT USED</t>
-        </is>
-      </c>
-      <c r="P69" s="11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q69" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="R69" s="11" t="inlineStr"/>
-      <c r="S69" s="11" t="inlineStr">
-        <is>
-          <t>Pawame|Active customers</t>
-        </is>
-      </c>
-      <c r="T69" s="11" t="inlineStr">
-        <is>
-          <t>SR17</t>
-        </is>
-      </c>
+      <c r="R69" s="7" t="inlineStr"/>
+      <c r="S69" s="7" t="inlineStr"/>
+      <c r="T69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>X-03</t>
+          <t>X-01</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>IFC / AFC material on PAYGo receivables financing</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
+          <t>Pawame SHS financed</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>18700</v>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>units</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>various</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Not identified</t>
+          <t>None found</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr"/>
@@ -6868,39 +6914,185 @@
       <c r="L70" s="11" t="inlineStr"/>
       <c r="M70" s="11" t="inlineStr">
         <is>
+          <t>No public source found</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O70" s="11" t="inlineStr">
+        <is>
+          <t>NOT USED</t>
+        </is>
+      </c>
+      <c r="P70" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q70" s="11" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="R70" s="11" t="inlineStr"/>
+      <c r="S70" s="11" t="inlineStr">
+        <is>
+          <t>Pawame|SHS financed</t>
+        </is>
+      </c>
+      <c r="T70" s="11" t="inlineStr">
+        <is>
+          <t>SR16</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>X-02</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Pawame active customers</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>customers</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr"/>
+      <c r="H71" s="11" t="inlineStr"/>
+      <c r="I71" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr"/>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>No public source found</t>
+        </is>
+      </c>
+      <c r="N71" s="11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O71" s="11" t="inlineStr">
+        <is>
+          <t>NOT USED</t>
+        </is>
+      </c>
+      <c r="P71" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q71" s="11" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="R71" s="11" t="inlineStr"/>
+      <c r="S71" s="11" t="inlineStr">
+        <is>
+          <t>Pawame|Active customers</t>
+        </is>
+      </c>
+      <c r="T71" s="11" t="inlineStr">
+        <is>
+          <t>SR17</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>X-03</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>IFC / AFC material on PAYGo receivables financing</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>Not identified</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="inlineStr"/>
+      <c r="H72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr"/>
+      <c r="L72" s="11" t="inlineStr"/>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
           <t>Listed for retrieval</t>
         </is>
       </c>
-      <c r="N70" s="11" t="inlineStr">
+      <c r="N72" s="11" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="O70" s="11" t="inlineStr">
+      <c r="O72" s="11" t="inlineStr">
         <is>
           <t>NOT USED</t>
         </is>
       </c>
-      <c r="P70" s="11" t="inlineStr">
+      <c r="P72" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Q70" s="11" t="inlineStr">
+      <c r="Q72" s="11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="R70" s="11" t="inlineStr"/>
-      <c r="S70" s="11" t="inlineStr"/>
-      <c r="T70" s="11" t="inlineStr">
+      <c r="R72" s="11" t="inlineStr"/>
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr">
         <is>
           <t>SR23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T70"/>
+  <autoFilter ref="A1:T72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7640,19 +7832,19 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>SR20</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>E3-01</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>PENDING PRIMARY DOCUMENT</t>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
